--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/MDPI-Xianshuihe_Datenbank/before_conversion_xian_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/MDPI-Xianshuihe_Datenbank/before_conversion_xian_mapped_readable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1176" uniqueCount="681">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1178" uniqueCount="682">
   <si>
     <t>location</t>
   </si>
@@ -104,6 +104,9 @@
   </si>
   <si>
     <t>Database_number</t>
+  </si>
+  <si>
+    <t>Database_name</t>
   </si>
   <si>
     <t>W1</t>
@@ -2420,7 +2423,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AD280"/>
+  <dimension ref="A1:AE280"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -2451,9 +2454,10 @@
     <col min="28" max="28" width="18.7109375" customWidth="1"/>
     <col min="29" max="29" width="14.7109375" customWidth="1"/>
     <col min="30" max="30" width="17.7109375" customWidth="1"/>
+    <col min="31" max="31" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30">
+    <row r="1" spans="1:31">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2544,10 +2548,13 @@
       <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="2" spans="1:30">
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31">
       <c r="B2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2">
         <v>31.79</v>
@@ -2556,13 +2563,13 @@
         <v>100.25</v>
       </c>
       <c r="H2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J2" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="N2">
         <v>68.41</v>
@@ -2589,9 +2596,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:30">
+    <row r="3" spans="1:31">
       <c r="B3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C3">
         <v>31.79</v>
@@ -2600,13 +2607,13 @@
         <v>100.25</v>
       </c>
       <c r="H3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="J3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N3">
         <v>83.405</v>
@@ -2633,9 +2640,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:30">
+    <row r="4" spans="1:31">
       <c r="B4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C4">
         <v>31.79</v>
@@ -2644,13 +2651,13 @@
         <v>100.25</v>
       </c>
       <c r="H4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="J4" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="N4">
         <v>68.04000000000001</v>
@@ -2677,9 +2684,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:30">
+    <row r="5" spans="1:31">
       <c r="B5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C5">
         <v>31.76</v>
@@ -2688,13 +2695,13 @@
         <v>100.29</v>
       </c>
       <c r="H5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J5" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N5">
         <v>2.749</v>
@@ -2721,9 +2728,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:30">
+    <row r="6" spans="1:31">
       <c r="B6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C6">
         <v>31.58</v>
@@ -2732,13 +2739,13 @@
         <v>100.43</v>
       </c>
       <c r="H6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="J6" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="N6">
         <v>13.495</v>
@@ -2765,18 +2772,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:30">
+    <row r="7" spans="1:31">
       <c r="B7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="J7" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N7">
         <v>15.472</v>
@@ -2803,9 +2810,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:30">
+    <row r="8" spans="1:31">
       <c r="B8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C8">
         <v>31.54</v>
@@ -2814,13 +2821,13 @@
         <v>100.46</v>
       </c>
       <c r="H8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J8" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="N8">
         <v>448.78</v>
@@ -2847,9 +2854,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:30">
+    <row r="9" spans="1:31">
       <c r="B9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C9">
         <v>31.54</v>
@@ -2858,13 +2865,13 @@
         <v>100.46</v>
       </c>
       <c r="H9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J9" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N9">
         <v>433.504</v>
@@ -2891,9 +2898,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:30">
+    <row r="10" spans="1:31">
       <c r="B10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C10">
         <v>31.54</v>
@@ -2902,13 +2909,13 @@
         <v>100.46</v>
       </c>
       <c r="H10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I10" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="J10" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="N10">
         <v>449.124</v>
@@ -2935,9 +2942,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:30">
+    <row r="11" spans="1:31">
       <c r="B11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C11">
         <v>31.58</v>
@@ -2946,13 +2953,13 @@
         <v>100.72</v>
       </c>
       <c r="H11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I11" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="J11" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="N11">
         <v>306.745</v>
@@ -2979,9 +2986,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:30">
+    <row r="12" spans="1:31">
       <c r="B12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C12">
         <v>31.58</v>
@@ -2990,13 +2997,13 @@
         <v>100.72</v>
       </c>
       <c r="H12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J12" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="N12">
         <v>372.217</v>
@@ -3023,9 +3030,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:30">
+    <row r="13" spans="1:31">
       <c r="B13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C13">
         <v>31.27</v>
@@ -3034,13 +3041,13 @@
         <v>100.8</v>
       </c>
       <c r="H13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I13" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="J13" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N13">
         <v>607.0700000000001</v>
@@ -3067,9 +3074,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:30">
+    <row r="14" spans="1:31">
       <c r="B14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C14">
         <v>31.27</v>
@@ -3078,13 +3085,13 @@
         <v>100.8</v>
       </c>
       <c r="H14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I14" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="J14" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N14">
         <v>619.72</v>
@@ -3111,9 +3118,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:30">
+    <row r="15" spans="1:31">
       <c r="B15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C15">
         <v>31.27</v>
@@ -3122,13 +3129,13 @@
         <v>100.8</v>
       </c>
       <c r="H15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I15" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="J15" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N15">
         <v>593.59</v>
@@ -3155,9 +3162,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:30">
+    <row r="16" spans="1:31">
       <c r="B16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C16">
         <v>31.27</v>
@@ -3166,13 +3173,13 @@
         <v>100.8</v>
       </c>
       <c r="H16" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I16" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J16" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="N16">
         <v>619.91</v>
@@ -3201,7 +3208,7 @@
     </row>
     <row r="17" spans="2:30">
       <c r="B17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C17">
         <v>31.27</v>
@@ -3210,13 +3217,13 @@
         <v>100.8</v>
       </c>
       <c r="H17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I17" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="J17" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N17">
         <v>876.182922395</v>
@@ -3242,7 +3249,7 @@
     </row>
     <row r="18" spans="2:30">
       <c r="B18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C18">
         <v>31.27</v>
@@ -3251,13 +3258,13 @@
         <v>100.8</v>
       </c>
       <c r="H18" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I18" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="J18" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="N18">
         <v>618.240735924</v>
@@ -3286,7 +3293,7 @@
     </row>
     <row r="19" spans="2:30">
       <c r="B19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C19">
         <v>31.27</v>
@@ -3295,13 +3302,13 @@
         <v>100.8</v>
       </c>
       <c r="H19" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I19" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J19" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N19">
         <v>660.0062804354829</v>
@@ -3330,7 +3337,7 @@
     </row>
     <row r="20" spans="2:30">
       <c r="B20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C20">
         <v>31.33</v>
@@ -3339,13 +3346,13 @@
         <v>100.9</v>
       </c>
       <c r="H20" t="s">
+        <v>93</v>
+      </c>
+      <c r="I20" t="s">
         <v>92</v>
       </c>
-      <c r="I20" t="s">
-        <v>91</v>
-      </c>
       <c r="J20" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N20">
         <v>402.443</v>
@@ -3374,7 +3381,7 @@
     </row>
     <row r="21" spans="2:30">
       <c r="B21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C21">
         <v>31.33</v>
@@ -3383,13 +3390,13 @@
         <v>100.9</v>
       </c>
       <c r="H21" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I21" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="J21" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="N21">
         <v>396.857</v>
@@ -3418,7 +3425,7 @@
     </row>
     <row r="22" spans="2:30">
       <c r="B22" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C22">
         <v>31.17</v>
@@ -3427,13 +3434,13 @@
         <v>100.92</v>
       </c>
       <c r="H22" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I22" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="J22" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="N22">
         <v>301.027</v>
@@ -3462,7 +3469,7 @@
     </row>
     <row r="23" spans="2:30">
       <c r="B23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C23">
         <v>31.17</v>
@@ -3471,13 +3478,13 @@
         <v>100.92</v>
       </c>
       <c r="H23" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I23" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J23" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="N23">
         <v>295.613</v>
@@ -3506,7 +3513,7 @@
     </row>
     <row r="24" spans="2:30">
       <c r="B24" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C24">
         <v>31.17</v>
@@ -3515,13 +3522,13 @@
         <v>100.92</v>
       </c>
       <c r="H24" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I24" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="J24" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N24">
         <v>287.125</v>
@@ -3550,7 +3557,7 @@
     </row>
     <row r="25" spans="2:30">
       <c r="B25" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C25">
         <v>31.17</v>
@@ -3559,13 +3566,13 @@
         <v>100.92</v>
       </c>
       <c r="H25" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I25" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="J25" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N25">
         <v>270.155</v>
@@ -3594,7 +3601,7 @@
     </row>
     <row r="26" spans="2:30">
       <c r="B26" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C26">
         <v>31.08</v>
@@ -3603,13 +3610,13 @@
         <v>101.01</v>
       </c>
       <c r="H26" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I26" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J26" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N26">
         <v>81.69600000000001</v>
@@ -3638,7 +3645,7 @@
     </row>
     <row r="27" spans="2:30">
       <c r="B27" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C27">
         <v>31.08</v>
@@ -3647,13 +3654,13 @@
         <v>101.01</v>
       </c>
       <c r="H27" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I27" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="J27" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N27">
         <v>79.572</v>
@@ -3682,7 +3689,7 @@
     </row>
     <row r="28" spans="2:30">
       <c r="B28" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C28">
         <v>31.08</v>
@@ -3691,13 +3698,13 @@
         <v>101.01</v>
       </c>
       <c r="H28" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I28" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J28" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N28">
         <v>77.64</v>
@@ -3726,7 +3733,7 @@
     </row>
     <row r="29" spans="2:30">
       <c r="B29" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C29">
         <v>31.07</v>
@@ -3735,13 +3742,13 @@
         <v>101.02</v>
       </c>
       <c r="H29" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I29" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="J29" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="N29">
         <v>31.22</v>
@@ -3770,7 +3777,7 @@
     </row>
     <row r="30" spans="2:30">
       <c r="B30" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C30">
         <v>31.01</v>
@@ -3779,13 +3786,13 @@
         <v>101.08</v>
       </c>
       <c r="H30" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I30" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J30" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N30">
         <v>16.57</v>
@@ -3814,7 +3821,7 @@
     </row>
     <row r="31" spans="2:30">
       <c r="B31" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C31">
         <v>31.01</v>
@@ -3823,13 +3830,13 @@
         <v>101.08</v>
       </c>
       <c r="H31" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I31" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="J31" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N31">
         <v>16.835</v>
@@ -3858,7 +3865,7 @@
     </row>
     <row r="32" spans="2:30">
       <c r="B32" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C32">
         <v>31.01</v>
@@ -3867,13 +3874,13 @@
         <v>101.08</v>
       </c>
       <c r="H32" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I32" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J32" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N32">
         <v>15.121</v>
@@ -3902,7 +3909,7 @@
     </row>
     <row r="33" spans="2:30">
       <c r="B33" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C33">
         <v>31.06</v>
@@ -3911,13 +3918,13 @@
         <v>101.1</v>
       </c>
       <c r="H33" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I33" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J33" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="N33">
         <v>494.378215234929</v>
@@ -3946,7 +3953,7 @@
     </row>
     <row r="34" spans="2:30">
       <c r="B34" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C34">
         <v>31.06</v>
@@ -3955,13 +3962,13 @@
         <v>101.1</v>
       </c>
       <c r="H34" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I34" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J34" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N34">
         <v>540.4010000000001</v>
@@ -3990,7 +3997,7 @@
     </row>
     <row r="35" spans="2:30">
       <c r="B35" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C35">
         <v>31.06</v>
@@ -3999,13 +4006,13 @@
         <v>101.1</v>
       </c>
       <c r="H35" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I35" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="J35" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N35">
         <v>538.619</v>
@@ -4034,7 +4041,7 @@
     </row>
     <row r="36" spans="2:30">
       <c r="B36" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C36">
         <v>31.06</v>
@@ -4043,13 +4050,13 @@
         <v>101.1</v>
       </c>
       <c r="H36" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I36" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J36" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N36">
         <v>551.7909999999999</v>
@@ -4078,7 +4085,7 @@
     </row>
     <row r="37" spans="2:30">
       <c r="B37" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C37">
         <v>31.06</v>
@@ -4087,13 +4094,13 @@
         <v>101.1</v>
       </c>
       <c r="H37" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I37" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J37" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N37">
         <v>530.293</v>
@@ -4122,7 +4129,7 @@
     </row>
     <row r="38" spans="2:30">
       <c r="B38" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C38">
         <v>31.18</v>
@@ -4131,13 +4138,13 @@
         <v>101.17</v>
       </c>
       <c r="H38" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I38" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="J38" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N38">
         <v>183.560762233806</v>
@@ -4166,7 +4173,7 @@
     </row>
     <row r="39" spans="2:30">
       <c r="B39" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C39">
         <v>31.18</v>
@@ -4175,13 +4182,13 @@
         <v>101.17</v>
       </c>
       <c r="H39" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I39" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J39" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N39">
         <v>189.444</v>
@@ -4210,7 +4217,7 @@
     </row>
     <row r="40" spans="2:30">
       <c r="B40" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C40">
         <v>31.28</v>
@@ -4219,13 +4226,13 @@
         <v>101.18</v>
       </c>
       <c r="H40" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I40" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="J40" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="N40">
         <v>213.264242178457</v>
@@ -4254,7 +4261,7 @@
     </row>
     <row r="41" spans="2:30">
       <c r="B41" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C41">
         <v>31.28</v>
@@ -4263,13 +4270,13 @@
         <v>101.18</v>
       </c>
       <c r="H41" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I41" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="J41" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N41">
         <v>224.145</v>
@@ -4298,7 +4305,7 @@
     </row>
     <row r="42" spans="2:30">
       <c r="B42" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C42">
         <v>31.14</v>
@@ -4307,13 +4314,13 @@
         <v>101.18</v>
       </c>
       <c r="H42" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I42" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="J42" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N42">
         <v>179.533228402099</v>
@@ -4342,7 +4349,7 @@
     </row>
     <row r="43" spans="2:30">
       <c r="B43" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C43">
         <v>31.14</v>
@@ -4351,13 +4358,13 @@
         <v>101.18</v>
       </c>
       <c r="H43" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I43" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="J43" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="N43">
         <v>153.556</v>
@@ -4386,7 +4393,7 @@
     </row>
     <row r="44" spans="2:30">
       <c r="B44" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C44">
         <v>30.95</v>
@@ -4395,13 +4402,13 @@
         <v>101.24</v>
       </c>
       <c r="H44" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I44" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J44" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="N44">
         <v>854</v>
@@ -4430,7 +4437,7 @@
     </row>
     <row r="45" spans="2:30">
       <c r="B45" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C45">
         <v>30.95</v>
@@ -4439,13 +4446,13 @@
         <v>101.24</v>
       </c>
       <c r="H45" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J45" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N45">
         <v>844.652772026</v>
@@ -4474,7 +4481,7 @@
     </row>
     <row r="46" spans="2:30">
       <c r="B46" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C46">
         <v>30.95</v>
@@ -4483,13 +4490,13 @@
         <v>101.24</v>
       </c>
       <c r="H46" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I46" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="J46" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="N46">
         <v>845.8969999999999</v>
@@ -4518,7 +4525,7 @@
     </row>
     <row r="47" spans="2:30">
       <c r="B47" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C47">
         <v>30.95</v>
@@ -4527,13 +4534,13 @@
         <v>101.24</v>
       </c>
       <c r="H47" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I47" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="J47" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="N47">
         <v>839</v>
@@ -4562,7 +4569,7 @@
     </row>
     <row r="48" spans="2:30">
       <c r="B48" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C48">
         <v>30.95</v>
@@ -4571,13 +4578,13 @@
         <v>101.24</v>
       </c>
       <c r="H48" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I48" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J48" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="N48">
         <v>891.152</v>
@@ -4606,7 +4613,7 @@
     </row>
     <row r="49" spans="2:30">
       <c r="B49" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C49">
         <v>30.95</v>
@@ -4615,13 +4622,13 @@
         <v>101.24</v>
       </c>
       <c r="H49" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I49" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J49" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N49">
         <v>859.674</v>
@@ -4650,7 +4657,7 @@
     </row>
     <row r="50" spans="2:30">
       <c r="B50" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C50">
         <v>30.95</v>
@@ -4659,13 +4666,13 @@
         <v>101.24</v>
       </c>
       <c r="H50" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I50" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J50" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="N50">
         <v>221.8</v>
@@ -4694,7 +4701,7 @@
     </row>
     <row r="51" spans="2:30">
       <c r="B51" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C51">
         <v>30.95</v>
@@ -4703,13 +4710,13 @@
         <v>101.24</v>
       </c>
       <c r="H51" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I51" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J51" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="N51">
         <v>205.03</v>
@@ -4738,7 +4745,7 @@
     </row>
     <row r="52" spans="2:30">
       <c r="B52" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C52">
         <v>30.95</v>
@@ -4747,13 +4754,13 @@
         <v>101.24</v>
       </c>
       <c r="H52" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I52" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="J52" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="N52">
         <v>198.93</v>
@@ -4782,7 +4789,7 @@
     </row>
     <row r="53" spans="2:30">
       <c r="B53" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C53">
         <v>30.95</v>
@@ -4791,13 +4798,13 @@
         <v>101.24</v>
       </c>
       <c r="H53" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I53" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="J53" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="N53">
         <v>176.77</v>
@@ -4826,7 +4833,7 @@
     </row>
     <row r="54" spans="2:30">
       <c r="B54" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C54">
         <v>30.95</v>
@@ -4835,13 +4842,13 @@
         <v>101.24</v>
       </c>
       <c r="H54" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I54" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="J54" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="N54">
         <v>227.774630136</v>
@@ -4870,7 +4877,7 @@
     </row>
     <row r="55" spans="2:30">
       <c r="B55" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C55">
         <v>30.95</v>
@@ -4879,13 +4886,13 @@
         <v>101.24</v>
       </c>
       <c r="H55" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I55" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="J55" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="N55">
         <v>259.59925453</v>
@@ -4914,7 +4921,7 @@
     </row>
     <row r="56" spans="2:30">
       <c r="B56" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C56">
         <v>30.95</v>
@@ -4923,13 +4930,13 @@
         <v>101.24</v>
       </c>
       <c r="H56" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I56" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J56" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N56">
         <v>239.722</v>
@@ -4958,7 +4965,7 @@
     </row>
     <row r="57" spans="2:30">
       <c r="B57" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C57">
         <v>30.95</v>
@@ -4967,13 +4974,13 @@
         <v>101.24</v>
       </c>
       <c r="H57" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I57" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J57" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="N57">
         <v>280.491</v>
@@ -5002,7 +5009,7 @@
     </row>
     <row r="58" spans="2:30">
       <c r="B58" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C58">
         <v>30.95</v>
@@ -5011,13 +5018,13 @@
         <v>101.24</v>
       </c>
       <c r="H58" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I58" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J58" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N58">
         <v>266.511</v>
@@ -5046,7 +5053,7 @@
     </row>
     <row r="59" spans="2:30">
       <c r="B59" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C59">
         <v>30.95</v>
@@ -5055,13 +5062,13 @@
         <v>101.24</v>
       </c>
       <c r="H59" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I59" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="J59" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="N59">
         <v>293.866</v>
@@ -5090,7 +5097,7 @@
     </row>
     <row r="60" spans="2:30">
       <c r="B60" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C60">
         <v>30.95</v>
@@ -5099,13 +5106,13 @@
         <v>101.24</v>
       </c>
       <c r="H60" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I60" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="J60" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N60">
         <v>267.166</v>
@@ -5134,7 +5141,7 @@
     </row>
     <row r="61" spans="2:30">
       <c r="B61" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C61">
         <v>30.95</v>
@@ -5143,13 +5150,13 @@
         <v>101.24</v>
       </c>
       <c r="H61" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I61" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="J61" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N61">
         <v>310.06</v>
@@ -5178,7 +5185,7 @@
     </row>
     <row r="62" spans="2:30">
       <c r="B62" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C62">
         <v>30.95</v>
@@ -5187,13 +5194,13 @@
         <v>101.24</v>
       </c>
       <c r="H62" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I62" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="J62" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N62">
         <v>288.86</v>
@@ -5222,7 +5229,7 @@
     </row>
     <row r="63" spans="2:30">
       <c r="B63" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C63">
         <v>30.95</v>
@@ -5231,13 +5238,13 @@
         <v>101.24</v>
       </c>
       <c r="H63" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I63" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="J63" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="N63">
         <v>280.27</v>
@@ -5266,7 +5273,7 @@
     </row>
     <row r="64" spans="2:30">
       <c r="B64" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C64">
         <v>30.95</v>
@@ -5275,13 +5282,13 @@
         <v>101.24</v>
       </c>
       <c r="H64" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I64" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="J64" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="N64">
         <v>281.7</v>
@@ -5310,7 +5317,7 @@
     </row>
     <row r="65" spans="2:30">
       <c r="B65" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C65">
         <v>30.95</v>
@@ -5319,13 +5326,13 @@
         <v>101.24</v>
       </c>
       <c r="H65" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I65" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="J65" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N65">
         <v>303.453234528</v>
@@ -5354,7 +5361,7 @@
     </row>
     <row r="66" spans="2:30">
       <c r="B66" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C66">
         <v>30.95</v>
@@ -5363,13 +5370,13 @@
         <v>101.24</v>
       </c>
       <c r="H66" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I66" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="J66" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="N66">
         <v>287.306077366</v>
@@ -5398,7 +5405,7 @@
     </row>
     <row r="67" spans="2:30">
       <c r="B67" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C67">
         <v>30.95</v>
@@ -5407,13 +5414,13 @@
         <v>101.24</v>
       </c>
       <c r="H67" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I67" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="J67" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="N67">
         <v>286.169</v>
@@ -5442,7 +5449,7 @@
     </row>
     <row r="68" spans="2:30">
       <c r="B68" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C68">
         <v>30.95</v>
@@ -5451,13 +5458,13 @@
         <v>101.24</v>
       </c>
       <c r="H68" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I68" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="J68" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="N68">
         <v>295.381</v>
@@ -5486,7 +5493,7 @@
     </row>
     <row r="69" spans="2:30">
       <c r="B69" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C69">
         <v>30.95</v>
@@ -5495,13 +5502,13 @@
         <v>101.24</v>
       </c>
       <c r="H69" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I69" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J69" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="N69">
         <v>158.977</v>
@@ -5530,7 +5537,7 @@
     </row>
     <row r="70" spans="2:30">
       <c r="B70" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C70">
         <v>30.95</v>
@@ -5539,13 +5546,13 @@
         <v>101.24</v>
       </c>
       <c r="H70" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I70" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="J70" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N70">
         <v>281.929</v>
@@ -5574,7 +5581,7 @@
     </row>
     <row r="71" spans="2:30">
       <c r="B71" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C71">
         <v>30.95</v>
@@ -5583,13 +5590,13 @@
         <v>101.24</v>
       </c>
       <c r="H71" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I71" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="J71" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N71">
         <v>290.776</v>
@@ -5618,7 +5625,7 @@
     </row>
     <row r="72" spans="2:30">
       <c r="B72" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C72">
         <v>30.86</v>
@@ -5627,13 +5634,13 @@
         <v>101.29</v>
       </c>
       <c r="H72" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I72" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="J72" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="N72">
         <v>112.508882122064</v>
@@ -5662,7 +5669,7 @@
     </row>
     <row r="73" spans="2:30">
       <c r="B73" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C73">
         <v>30.86</v>
@@ -5671,13 +5678,13 @@
         <v>101.29</v>
       </c>
       <c r="H73" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I73" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="J73" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="N73">
         <v>115.738</v>
@@ -5706,7 +5713,7 @@
     </row>
     <row r="74" spans="2:30">
       <c r="B74" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C74">
         <v>30.86</v>
@@ -5715,13 +5722,13 @@
         <v>101.29</v>
       </c>
       <c r="H74" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I74" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="J74" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="N74">
         <v>117.333</v>
@@ -5750,7 +5757,7 @@
     </row>
     <row r="75" spans="2:30">
       <c r="B75" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C75">
         <v>30.86</v>
@@ -5759,13 +5766,13 @@
         <v>101.29</v>
       </c>
       <c r="H75" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I75" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J75" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="N75">
         <v>117.791</v>
@@ -5794,7 +5801,7 @@
     </row>
     <row r="76" spans="2:30">
       <c r="B76" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C76">
         <v>30.86</v>
@@ -5803,13 +5810,13 @@
         <v>101.29</v>
       </c>
       <c r="H76" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I76" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="J76" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="N76">
         <v>114.213</v>
@@ -5838,7 +5845,7 @@
     </row>
     <row r="77" spans="2:30">
       <c r="B77" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C77">
         <v>31.04</v>
@@ -5847,13 +5854,13 @@
         <v>101.4</v>
       </c>
       <c r="H77" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I77" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="J77" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N77">
         <v>221.437023331912</v>
@@ -5882,7 +5889,7 @@
     </row>
     <row r="78" spans="2:30">
       <c r="B78" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C78">
         <v>30.49</v>
@@ -5891,13 +5898,13 @@
         <v>101.53</v>
       </c>
       <c r="H78" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I78" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J78" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="N78">
         <v>124.988</v>
@@ -5926,7 +5933,7 @@
     </row>
     <row r="79" spans="2:30">
       <c r="B79" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C79">
         <v>30.49</v>
@@ -5935,13 +5942,13 @@
         <v>101.53</v>
       </c>
       <c r="H79" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I79" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="J79" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N79">
         <v>118.584</v>
@@ -5970,7 +5977,7 @@
     </row>
     <row r="80" spans="2:30">
       <c r="B80" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C80">
         <v>30.49</v>
@@ -5979,13 +5986,13 @@
         <v>101.53</v>
       </c>
       <c r="H80" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I80" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="J80" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N80">
         <v>113.311</v>
@@ -6014,7 +6021,7 @@
     </row>
     <row r="81" spans="2:30">
       <c r="B81" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C81">
         <v>30.54</v>
@@ -6023,13 +6030,13 @@
         <v>101.62</v>
       </c>
       <c r="H81" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I81" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="J81" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N81">
         <v>443</v>
@@ -6058,7 +6065,7 @@
     </row>
     <row r="82" spans="2:30">
       <c r="B82" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C82">
         <v>30.54</v>
@@ -6067,13 +6074,13 @@
         <v>101.62</v>
       </c>
       <c r="H82" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I82" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="J82" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N82">
         <v>417.075</v>
@@ -6102,7 +6109,7 @@
     </row>
     <row r="83" spans="2:30">
       <c r="B83" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C83">
         <v>30.54</v>
@@ -6111,13 +6118,13 @@
         <v>101.62</v>
       </c>
       <c r="H83" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I83" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="J83" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="N83">
         <v>463.31</v>
@@ -6146,7 +6153,7 @@
     </row>
     <row r="84" spans="2:30">
       <c r="B84" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C84">
         <v>30.54</v>
@@ -6155,13 +6162,13 @@
         <v>101.62</v>
       </c>
       <c r="H84" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I84" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J84" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="N84">
         <v>679.23</v>
@@ -6190,7 +6197,7 @@
     </row>
     <row r="85" spans="2:30">
       <c r="B85" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C85">
         <v>30.54</v>
@@ -6199,13 +6206,13 @@
         <v>101.62</v>
       </c>
       <c r="H85" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I85" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="J85" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N85">
         <v>464.650475685</v>
@@ -6234,7 +6241,7 @@
     </row>
     <row r="86" spans="2:30">
       <c r="B86" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C86">
         <v>30.54</v>
@@ -6243,13 +6250,13 @@
         <v>101.62</v>
       </c>
       <c r="H86" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I86" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="J86" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N86">
         <v>459.001012792</v>
@@ -6278,7 +6285,7 @@
     </row>
     <row r="87" spans="2:30">
       <c r="B87" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C87">
         <v>30.54</v>
@@ -6287,13 +6294,13 @@
         <v>101.62</v>
       </c>
       <c r="H87" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I87" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="J87" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="N87">
         <v>435.318700827626</v>
@@ -6322,7 +6329,7 @@
     </row>
     <row r="88" spans="2:30">
       <c r="B88" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C88">
         <v>30.54</v>
@@ -6331,13 +6338,13 @@
         <v>101.62</v>
       </c>
       <c r="H88" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I88" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="J88" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="N88">
         <v>469.202</v>
@@ -6366,7 +6373,7 @@
     </row>
     <row r="89" spans="2:30">
       <c r="B89" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C89">
         <v>30.54</v>
@@ -6375,13 +6382,13 @@
         <v>101.62</v>
       </c>
       <c r="H89" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I89" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="J89" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N89">
         <v>412.587</v>
@@ -6410,7 +6417,7 @@
     </row>
     <row r="90" spans="2:30">
       <c r="B90" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C90">
         <v>30.54</v>
@@ -6419,13 +6426,13 @@
         <v>101.62</v>
       </c>
       <c r="H90" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I90" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J90" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="N90">
         <v>384.701</v>
@@ -6454,7 +6461,7 @@
     </row>
     <row r="91" spans="2:30">
       <c r="B91" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C91">
         <v>30.54</v>
@@ -6463,13 +6470,13 @@
         <v>101.62</v>
       </c>
       <c r="H91" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I91" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="J91" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="N91">
         <v>386.64</v>
@@ -6498,7 +6505,7 @@
     </row>
     <row r="92" spans="2:30">
       <c r="B92" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C92">
         <v>30.54</v>
@@ -6507,13 +6514,13 @@
         <v>101.62</v>
       </c>
       <c r="H92" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I92" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="J92" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="N92">
         <v>472.388</v>
@@ -6542,7 +6549,7 @@
     </row>
     <row r="93" spans="2:30">
       <c r="B93" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C93">
         <v>30.55</v>
@@ -6551,13 +6558,13 @@
         <v>101.62</v>
       </c>
       <c r="H93" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I93" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="J93" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="N93">
         <v>305.870321755855</v>
@@ -6586,7 +6593,7 @@
     </row>
     <row r="94" spans="2:30">
       <c r="B94" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C94">
         <v>30.55</v>
@@ -6595,13 +6602,13 @@
         <v>101.62</v>
       </c>
       <c r="H94" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I94" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="J94" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="N94">
         <v>277.538</v>
@@ -6630,7 +6637,7 @@
     </row>
     <row r="95" spans="2:30">
       <c r="B95" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C95">
         <v>30.55</v>
@@ -6639,13 +6646,13 @@
         <v>101.62</v>
       </c>
       <c r="H95" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I95" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="J95" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="N95">
         <v>286.592</v>
@@ -6674,7 +6681,7 @@
     </row>
     <row r="96" spans="2:30">
       <c r="B96" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C96">
         <v>30.55</v>
@@ -6683,13 +6690,13 @@
         <v>101.62</v>
       </c>
       <c r="H96" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I96" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J96" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="N96">
         <v>295.134</v>
@@ -6718,7 +6725,7 @@
     </row>
     <row r="97" spans="2:30">
       <c r="B97" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C97">
         <v>30.55</v>
@@ -6727,13 +6734,13 @@
         <v>101.62</v>
       </c>
       <c r="H97" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I97" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="J97" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N97">
         <v>285.607</v>
@@ -6762,7 +6769,7 @@
     </row>
     <row r="98" spans="2:30">
       <c r="B98" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C98">
         <v>30.55</v>
@@ -6771,13 +6778,13 @@
         <v>101.62</v>
       </c>
       <c r="H98" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I98" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J98" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="N98">
         <v>284.95</v>
@@ -6806,7 +6813,7 @@
     </row>
     <row r="99" spans="2:30">
       <c r="B99" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C99">
         <v>30.28</v>
@@ -6815,13 +6822,13 @@
         <v>101.84</v>
       </c>
       <c r="H99" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I99" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="J99" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N99">
         <v>171.479</v>
@@ -6850,7 +6857,7 @@
     </row>
     <row r="100" spans="2:30">
       <c r="B100" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C100">
         <v>30.28</v>
@@ -6859,13 +6866,13 @@
         <v>101.84</v>
       </c>
       <c r="H100" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I100" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="J100" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="N100">
         <v>165.526</v>
@@ -6894,7 +6901,7 @@
     </row>
     <row r="101" spans="2:30">
       <c r="B101" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C101">
         <v>30.28</v>
@@ -6903,13 +6910,13 @@
         <v>101.84</v>
       </c>
       <c r="H101" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I101" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="J101" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="N101">
         <v>225.555</v>
@@ -6938,7 +6945,7 @@
     </row>
     <row r="102" spans="2:30">
       <c r="B102" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C102">
         <v>30.28</v>
@@ -6947,13 +6954,13 @@
         <v>101.84</v>
       </c>
       <c r="H102" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I102" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="J102" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="N102">
         <v>216.85</v>
@@ -6982,7 +6989,7 @@
     </row>
     <row r="103" spans="2:30">
       <c r="B103" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C103">
         <v>30.01</v>
@@ -6991,13 +6998,13 @@
         <v>101.86</v>
       </c>
       <c r="H103" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I103" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="J103" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N103">
         <v>208.79</v>
@@ -7026,7 +7033,7 @@
     </row>
     <row r="104" spans="2:30">
       <c r="B104" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C104">
         <v>30.01</v>
@@ -7035,13 +7042,13 @@
         <v>101.86</v>
       </c>
       <c r="H104" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I104" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="J104" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N104">
         <v>219.828</v>
@@ -7070,7 +7077,7 @@
     </row>
     <row r="105" spans="2:30">
       <c r="B105" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C105">
         <v>30.01</v>
@@ -7079,13 +7086,13 @@
         <v>101.86</v>
       </c>
       <c r="H105" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I105" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="J105" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="N105">
         <v>207.09</v>
@@ -7114,7 +7121,7 @@
     </row>
     <row r="106" spans="2:30">
       <c r="B106" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C106">
         <v>30.01</v>
@@ -7123,13 +7130,13 @@
         <v>101.86</v>
       </c>
       <c r="H106" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I106" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="J106" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="N106">
         <v>208.84</v>
@@ -7158,7 +7165,7 @@
     </row>
     <row r="107" spans="2:30">
       <c r="B107" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C107">
         <v>30.01</v>
@@ -7167,13 +7174,13 @@
         <v>101.86</v>
       </c>
       <c r="H107" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I107" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="J107" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N107">
         <v>218.153240305</v>
@@ -7202,7 +7209,7 @@
     </row>
     <row r="108" spans="2:30">
       <c r="B108" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C108">
         <v>30.01</v>
@@ -7211,13 +7218,13 @@
         <v>101.86</v>
       </c>
       <c r="H108" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I108" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="J108" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N108">
         <v>207.346458522</v>
@@ -7246,7 +7253,7 @@
     </row>
     <row r="109" spans="2:30">
       <c r="B109" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C109">
         <v>30.01</v>
@@ -7255,13 +7262,13 @@
         <v>101.86</v>
       </c>
       <c r="H109" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I109" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="J109" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="N109">
         <v>212.81</v>
@@ -7290,7 +7297,7 @@
     </row>
     <row r="110" spans="2:30">
       <c r="B110" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C110">
         <v>30.01</v>
@@ -7299,13 +7306,13 @@
         <v>101.86</v>
       </c>
       <c r="H110" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I110" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="J110" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="N110">
         <v>211.929</v>
@@ -7331,7 +7338,7 @@
     </row>
     <row r="111" spans="2:30">
       <c r="B111" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C111">
         <v>30.01</v>
@@ -7340,13 +7347,13 @@
         <v>101.86</v>
       </c>
       <c r="H111" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I111" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="J111" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="N111">
         <v>257.716</v>
@@ -7372,7 +7379,7 @@
     </row>
     <row r="112" spans="2:30">
       <c r="B112" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C112">
         <v>30.01</v>
@@ -7381,13 +7388,13 @@
         <v>101.86</v>
       </c>
       <c r="H112" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I112" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="J112" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="N112">
         <v>207.336</v>
@@ -7416,7 +7423,7 @@
     </row>
     <row r="113" spans="2:30">
       <c r="B113" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C113">
         <v>30.01</v>
@@ -7425,13 +7432,13 @@
         <v>101.86</v>
       </c>
       <c r="H113" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I113" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="J113" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="N113">
         <v>170.878</v>
@@ -7460,7 +7467,7 @@
     </row>
     <row r="114" spans="2:30">
       <c r="B114" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C114">
         <v>30.01</v>
@@ -7469,13 +7476,13 @@
         <v>101.86</v>
       </c>
       <c r="H114" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I114" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="J114" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="N114">
         <v>167.189</v>
@@ -7504,7 +7511,7 @@
     </row>
     <row r="115" spans="2:30">
       <c r="B115" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C115">
         <v>30.01</v>
@@ -7513,13 +7520,13 @@
         <v>101.86</v>
       </c>
       <c r="H115" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I115" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="J115" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N115">
         <v>173.823</v>
@@ -7548,7 +7555,7 @@
     </row>
     <row r="116" spans="2:30">
       <c r="B116" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C116">
         <v>30.01</v>
@@ -7557,13 +7564,13 @@
         <v>101.86</v>
       </c>
       <c r="H116" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I116" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="J116" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="N116">
         <v>151.26</v>
@@ -7592,7 +7599,7 @@
     </row>
     <row r="117" spans="2:30">
       <c r="B117" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C117">
         <v>30.01</v>
@@ -7601,13 +7608,13 @@
         <v>101.86</v>
       </c>
       <c r="H117" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I117" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="J117" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="N117">
         <v>166.711</v>
@@ -7636,7 +7643,7 @@
     </row>
     <row r="118" spans="2:30">
       <c r="B118" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C118">
         <v>30.01</v>
@@ -7645,13 +7652,13 @@
         <v>101.86</v>
       </c>
       <c r="H118" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I118" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="J118" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="N118">
         <v>163.071</v>
@@ -7680,7 +7687,7 @@
     </row>
     <row r="119" spans="2:30">
       <c r="B119" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C119">
         <v>30.27</v>
@@ -7689,13 +7696,13 @@
         <v>101.87</v>
       </c>
       <c r="H119" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I119" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="J119" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="N119">
         <v>268.652933868259</v>
@@ -7724,7 +7731,7 @@
     </row>
     <row r="120" spans="2:30">
       <c r="B120" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C120">
         <v>30.27</v>
@@ -7733,13 +7740,13 @@
         <v>101.87</v>
       </c>
       <c r="H120" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I120" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="J120" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="N120">
         <v>296.171</v>
@@ -7768,7 +7775,7 @@
     </row>
     <row r="121" spans="2:30">
       <c r="B121" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C121">
         <v>30.27</v>
@@ -7777,13 +7784,13 @@
         <v>101.87</v>
       </c>
       <c r="H121" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I121" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="J121" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="N121">
         <v>294.151</v>
@@ -7812,7 +7819,7 @@
     </row>
     <row r="122" spans="2:30">
       <c r="B122" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C122">
         <v>30.27</v>
@@ -7821,13 +7828,13 @@
         <v>101.87</v>
       </c>
       <c r="H122" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I122" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="J122" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N122">
         <v>307.473</v>
@@ -7856,7 +7863,7 @@
     </row>
     <row r="123" spans="2:30">
       <c r="B123" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C123">
         <v>30.27</v>
@@ -7865,13 +7872,13 @@
         <v>101.87</v>
       </c>
       <c r="H123" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I123" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J123" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="N123">
         <v>273.227</v>
@@ -7900,7 +7907,7 @@
     </row>
     <row r="124" spans="2:30">
       <c r="B124" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C124">
         <v>30.27</v>
@@ -7909,13 +7916,13 @@
         <v>101.87</v>
       </c>
       <c r="H124" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I124" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="J124" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="N124">
         <v>250.779</v>
@@ -7944,7 +7951,7 @@
     </row>
     <row r="125" spans="2:30">
       <c r="B125" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C125">
         <v>30.27</v>
@@ -7953,13 +7960,13 @@
         <v>101.87</v>
       </c>
       <c r="H125" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I125" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="J125" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="N125">
         <v>297.338</v>
@@ -7988,7 +7995,7 @@
     </row>
     <row r="126" spans="2:30">
       <c r="B126" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C126">
         <v>30.17</v>
@@ -7997,13 +8004,13 @@
         <v>101.87</v>
       </c>
       <c r="H126" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I126" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="J126" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="N126">
         <v>179.578402708277</v>
@@ -8032,7 +8039,7 @@
     </row>
     <row r="127" spans="2:30">
       <c r="B127" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C127">
         <v>30.17</v>
@@ -8041,13 +8048,13 @@
         <v>101.87</v>
       </c>
       <c r="H127" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I127" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="J127" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="N127">
         <v>187.54</v>
@@ -8076,7 +8083,7 @@
     </row>
     <row r="128" spans="2:30">
       <c r="B128" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C128">
         <v>30.17</v>
@@ -8085,13 +8092,13 @@
         <v>101.87</v>
       </c>
       <c r="H128" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I128" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J128" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="N128">
         <v>167.795</v>
@@ -8120,7 +8127,7 @@
     </row>
     <row r="129" spans="2:30">
       <c r="B129" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C129">
         <v>30.17</v>
@@ -8129,13 +8136,13 @@
         <v>101.87</v>
       </c>
       <c r="H129" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I129" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="J129" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="N129">
         <v>165.618</v>
@@ -8164,7 +8171,7 @@
     </row>
     <row r="130" spans="2:30">
       <c r="B130" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C130">
         <v>30.17</v>
@@ -8173,13 +8180,13 @@
         <v>101.87</v>
       </c>
       <c r="H130" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I130" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J130" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="N130">
         <v>169.914</v>
@@ -8208,7 +8215,7 @@
     </row>
     <row r="131" spans="2:30">
       <c r="B131" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C131">
         <v>30.17</v>
@@ -8217,13 +8224,13 @@
         <v>101.87</v>
       </c>
       <c r="H131" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I131" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J131" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="N131">
         <v>165.36</v>
@@ -8252,7 +8259,7 @@
     </row>
     <row r="132" spans="2:30">
       <c r="B132" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C132">
         <v>30.17</v>
@@ -8261,13 +8268,13 @@
         <v>101.87</v>
       </c>
       <c r="H132" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I132" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="J132" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="N132">
         <v>157.182</v>
@@ -8296,7 +8303,7 @@
     </row>
     <row r="133" spans="2:30">
       <c r="B133" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C133">
         <v>30.25</v>
@@ -8305,13 +8312,13 @@
         <v>101.88</v>
       </c>
       <c r="H133" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I133" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J133" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="N133">
         <v>377.437</v>
@@ -8340,7 +8347,7 @@
     </row>
     <row r="134" spans="2:30">
       <c r="B134" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C134">
         <v>30.25</v>
@@ -8349,13 +8356,13 @@
         <v>101.88</v>
       </c>
       <c r="H134" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I134" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J134" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="N134">
         <v>390.081</v>
@@ -8384,7 +8391,7 @@
     </row>
     <row r="135" spans="2:30">
       <c r="B135" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C135">
         <v>30.25</v>
@@ -8393,13 +8400,13 @@
         <v>101.88</v>
       </c>
       <c r="H135" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I135" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J135" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="N135">
         <v>378.652</v>
@@ -8428,7 +8435,7 @@
     </row>
     <row r="136" spans="2:30">
       <c r="B136" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C136">
         <v>30.25</v>
@@ -8437,13 +8444,13 @@
         <v>101.88</v>
       </c>
       <c r="H136" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I136" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="J136" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="N136">
         <v>394.225</v>
@@ -8472,7 +8479,7 @@
     </row>
     <row r="137" spans="2:30">
       <c r="B137" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C137">
         <v>30.25</v>
@@ -8481,13 +8488,13 @@
         <v>101.88</v>
       </c>
       <c r="H137" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I137" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="J137" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N137">
         <v>282.342021043104</v>
@@ -8516,7 +8523,7 @@
     </row>
     <row r="138" spans="2:30">
       <c r="B138" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C138">
         <v>30.25</v>
@@ -8525,13 +8532,13 @@
         <v>101.88</v>
       </c>
       <c r="H138" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I138" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="J138" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="N138">
         <v>326.873</v>
@@ -8560,7 +8567,7 @@
     </row>
     <row r="139" spans="2:30">
       <c r="B139" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C139">
         <v>30.25</v>
@@ -8569,13 +8576,13 @@
         <v>101.88</v>
       </c>
       <c r="H139" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I139" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="J139" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="N139">
         <v>336.516</v>
@@ -8604,7 +8611,7 @@
     </row>
     <row r="140" spans="2:30">
       <c r="B140" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C140">
         <v>30.25</v>
@@ -8613,13 +8620,13 @@
         <v>101.88</v>
       </c>
       <c r="H140" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I140" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J140" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="N140">
         <v>312.11</v>
@@ -8648,7 +8655,7 @@
     </row>
     <row r="141" spans="2:30">
       <c r="B141" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C141">
         <v>30.25</v>
@@ -8657,13 +8664,13 @@
         <v>101.88</v>
       </c>
       <c r="H141" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I141" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="J141" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="N141">
         <v>322.421</v>
@@ -8692,7 +8699,7 @@
     </row>
     <row r="142" spans="2:30">
       <c r="B142" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C142">
         <v>30.25</v>
@@ -8701,13 +8708,13 @@
         <v>101.88</v>
       </c>
       <c r="H142" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I142" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="J142" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="N142">
         <v>290.267</v>
@@ -8736,7 +8743,7 @@
     </row>
     <row r="143" spans="2:30">
       <c r="B143" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C143">
         <v>30.09</v>
@@ -8745,13 +8752,13 @@
         <v>101.95</v>
       </c>
       <c r="H143" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I143" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="J143" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="N143">
         <v>150.532</v>
@@ -8780,7 +8787,7 @@
     </row>
     <row r="144" spans="2:30">
       <c r="B144" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C144">
         <v>30.09</v>
@@ -8789,13 +8796,13 @@
         <v>101.95</v>
       </c>
       <c r="H144" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I144" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J144" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="N144">
         <v>150.67</v>
@@ -8824,7 +8831,7 @@
     </row>
     <row r="145" spans="2:30">
       <c r="B145" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C145">
         <v>30.09</v>
@@ -8833,13 +8840,13 @@
         <v>101.95</v>
       </c>
       <c r="H145" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I145" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J145" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="N145">
         <v>146.31</v>
@@ -8868,7 +8875,7 @@
     </row>
     <row r="146" spans="2:30">
       <c r="B146" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C146">
         <v>30.09</v>
@@ -8877,13 +8884,13 @@
         <v>101.95</v>
       </c>
       <c r="H146" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I146" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="J146" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N146">
         <v>157.07</v>
@@ -8912,7 +8919,7 @@
     </row>
     <row r="147" spans="2:30">
       <c r="B147" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C147">
         <v>30.09</v>
@@ -8921,13 +8928,13 @@
         <v>101.95</v>
       </c>
       <c r="H147" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I147" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="J147" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="N147">
         <v>170.146027712</v>
@@ -8956,7 +8963,7 @@
     </row>
     <row r="148" spans="2:30">
       <c r="B148" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C148">
         <v>30.09</v>
@@ -8965,13 +8972,13 @@
         <v>101.95</v>
       </c>
       <c r="H148" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I148" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="J148" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="N148">
         <v>156.117191958</v>
@@ -9000,7 +9007,7 @@
     </row>
     <row r="149" spans="2:30">
       <c r="B149" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C149">
         <v>30.09</v>
@@ -9009,13 +9016,13 @@
         <v>101.95</v>
       </c>
       <c r="H149" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I149" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="J149" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="N149">
         <v>159.277740416163</v>
@@ -9044,7 +9051,7 @@
     </row>
     <row r="150" spans="2:30">
       <c r="B150" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C150">
         <v>30.09</v>
@@ -9053,13 +9060,13 @@
         <v>101.95</v>
       </c>
       <c r="H150" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I150" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="J150" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N150">
         <v>144.144</v>
@@ -9088,7 +9095,7 @@
     </row>
     <row r="151" spans="2:30">
       <c r="B151" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C151">
         <v>30.09</v>
@@ -9097,13 +9104,13 @@
         <v>101.95</v>
       </c>
       <c r="H151" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I151" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J151" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="N151">
         <v>158.282</v>
@@ -9132,7 +9139,7 @@
     </row>
     <row r="152" spans="2:30">
       <c r="B152" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C152">
         <v>30.09</v>
@@ -9141,13 +9148,13 @@
         <v>101.95</v>
       </c>
       <c r="H152" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I152" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J152" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="N152">
         <v>163.589</v>
@@ -9176,7 +9183,7 @@
     </row>
     <row r="153" spans="2:30">
       <c r="B153" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C153">
         <v>30.09</v>
@@ -9185,13 +9192,13 @@
         <v>101.95</v>
       </c>
       <c r="H153" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I153" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="J153" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="N153">
         <v>134.733</v>
@@ -9220,7 +9227,7 @@
     </row>
     <row r="154" spans="2:30">
       <c r="B154" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C154">
         <v>30.09</v>
@@ -9229,13 +9236,13 @@
         <v>101.95</v>
       </c>
       <c r="H154" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I154" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="J154" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="N154">
         <v>155.581</v>
@@ -9264,7 +9271,7 @@
     </row>
     <row r="155" spans="2:30">
       <c r="B155" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C155">
         <v>30.09</v>
@@ -9273,13 +9280,13 @@
         <v>101.95</v>
       </c>
       <c r="H155" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I155" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="J155" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N155">
         <v>137.812</v>
@@ -9308,7 +9315,7 @@
     </row>
     <row r="156" spans="2:30">
       <c r="B156" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C156">
         <v>30.09</v>
@@ -9317,13 +9324,13 @@
         <v>101.95</v>
       </c>
       <c r="H156" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I156" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J156" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="N156">
         <v>133.273</v>
@@ -9352,7 +9359,7 @@
     </row>
     <row r="157" spans="2:30">
       <c r="B157" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C157">
         <v>30.09</v>
@@ -9361,13 +9368,13 @@
         <v>101.95</v>
       </c>
       <c r="H157" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I157" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="J157" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="N157">
         <v>133.655</v>
@@ -9396,7 +9403,7 @@
     </row>
     <row r="158" spans="2:30">
       <c r="B158" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C158">
         <v>30.09</v>
@@ -9405,13 +9412,13 @@
         <v>101.95</v>
       </c>
       <c r="H158" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I158" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="J158" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="N158">
         <v>131.668</v>
@@ -9440,7 +9447,7 @@
     </row>
     <row r="159" spans="2:30">
       <c r="B159" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C159">
         <v>30.09</v>
@@ -9449,13 +9456,13 @@
         <v>101.95</v>
       </c>
       <c r="H159" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I159" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="J159" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="N159">
         <v>137.64</v>
@@ -9484,7 +9491,7 @@
     </row>
     <row r="160" spans="2:30">
       <c r="B160" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C160">
         <v>29.98</v>
@@ -9493,13 +9500,13 @@
         <v>101.96</v>
       </c>
       <c r="H160" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I160" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="J160" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="N160">
         <v>510.82</v>
@@ -9528,7 +9535,7 @@
     </row>
     <row r="161" spans="2:30">
       <c r="B161" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C161">
         <v>29.98</v>
@@ -9537,13 +9544,13 @@
         <v>101.96</v>
       </c>
       <c r="H161" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I161" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="J161" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="N161">
         <v>518.38</v>
@@ -9572,7 +9579,7 @@
     </row>
     <row r="162" spans="2:30">
       <c r="B162" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C162">
         <v>29.98</v>
@@ -9581,13 +9588,13 @@
         <v>101.96</v>
       </c>
       <c r="H162" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I162" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="J162" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="N162">
         <v>516.6799999999999</v>
@@ -9616,7 +9623,7 @@
     </row>
     <row r="163" spans="2:30">
       <c r="B163" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C163">
         <v>29.98</v>
@@ -9625,13 +9632,13 @@
         <v>101.96</v>
       </c>
       <c r="H163" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I163" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="J163" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="N163">
         <v>507.94</v>
@@ -9660,7 +9667,7 @@
     </row>
     <row r="164" spans="2:30">
       <c r="B164" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C164">
         <v>29.98</v>
@@ -9669,13 +9676,13 @@
         <v>101.96</v>
       </c>
       <c r="H164" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I164" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="J164" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="N164">
         <v>513.624532465</v>
@@ -9704,7 +9711,7 @@
     </row>
     <row r="165" spans="2:30">
       <c r="B165" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C165">
         <v>29.98</v>
@@ -9713,13 +9720,13 @@
         <v>101.96</v>
       </c>
       <c r="H165" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I165" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J165" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="N165">
         <v>506.564477146</v>
@@ -9748,7 +9755,7 @@
     </row>
     <row r="166" spans="2:30">
       <c r="B166" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C166">
         <v>29.98</v>
@@ -9757,13 +9764,13 @@
         <v>101.96</v>
       </c>
       <c r="H166" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I166" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J166" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="N166">
         <v>501.990598536208</v>
@@ -9792,7 +9799,7 @@
     </row>
     <row r="167" spans="2:30">
       <c r="B167" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C167">
         <v>29.98</v>
@@ -9801,13 +9808,13 @@
         <v>101.96</v>
       </c>
       <c r="H167" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I167" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="J167" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="N167">
         <v>513.324</v>
@@ -9836,7 +9843,7 @@
     </row>
     <row r="168" spans="2:30">
       <c r="B168" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C168">
         <v>29.98</v>
@@ -9845,13 +9852,13 @@
         <v>101.96</v>
       </c>
       <c r="H168" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I168" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="J168" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N168">
         <v>516.519</v>
@@ -9880,7 +9887,7 @@
     </row>
     <row r="169" spans="2:30">
       <c r="B169" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C169">
         <v>29.98</v>
@@ -9889,13 +9896,13 @@
         <v>101.96</v>
       </c>
       <c r="H169" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I169" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="J169" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="N169">
         <v>506.757</v>
@@ -9924,7 +9931,7 @@
     </row>
     <row r="170" spans="2:30">
       <c r="B170" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C170">
         <v>29.98</v>
@@ -9933,13 +9940,13 @@
         <v>101.96</v>
       </c>
       <c r="H170" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I170" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="J170" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="N170">
         <v>493.142</v>
@@ -9968,7 +9975,7 @@
     </row>
     <row r="171" spans="2:30">
       <c r="B171" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C171">
         <v>29.98</v>
@@ -9977,13 +9984,13 @@
         <v>101.96</v>
       </c>
       <c r="H171" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I171" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="J171" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="N171">
         <v>511.2619999999999</v>
@@ -10012,7 +10019,7 @@
     </row>
     <row r="172" spans="2:30">
       <c r="B172" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C172">
         <v>29.98</v>
@@ -10021,13 +10028,13 @@
         <v>101.96</v>
       </c>
       <c r="H172" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I172" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="J172" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="N172">
         <v>506.1180000000001</v>
@@ -10056,7 +10063,7 @@
     </row>
     <row r="173" spans="2:30">
       <c r="B173" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C173">
         <v>29.98</v>
@@ -10065,13 +10072,13 @@
         <v>101.96</v>
       </c>
       <c r="H173" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I173" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J173" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="N173">
         <v>520.561</v>
@@ -10100,7 +10107,7 @@
     </row>
     <row r="174" spans="2:30">
       <c r="B174" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C174">
         <v>29.98</v>
@@ -10109,13 +10116,13 @@
         <v>101.96</v>
       </c>
       <c r="H174" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I174" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="J174" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="N174">
         <v>518.9110000000001</v>
@@ -10144,7 +10151,7 @@
     </row>
     <row r="175" spans="2:30">
       <c r="B175" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C175">
         <v>29.98</v>
@@ -10153,13 +10160,13 @@
         <v>101.96</v>
       </c>
       <c r="H175" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I175" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="J175" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="N175">
         <v>505.442</v>
@@ -10188,7 +10195,7 @@
     </row>
     <row r="176" spans="2:30">
       <c r="B176" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C176">
         <v>29.98</v>
@@ -10197,13 +10204,13 @@
         <v>101.96</v>
       </c>
       <c r="H176" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I176" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="J176" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N176">
         <v>526.635</v>
@@ -10232,7 +10239,7 @@
     </row>
     <row r="177" spans="2:30">
       <c r="B177" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C177">
         <v>29.97</v>
@@ -10241,13 +10248,13 @@
         <v>101.96</v>
       </c>
       <c r="H177" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I177" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J177" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="N177">
         <v>533.112</v>
@@ -10276,7 +10283,7 @@
     </row>
     <row r="178" spans="2:30">
       <c r="B178" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C178">
         <v>29.39</v>
@@ -10285,13 +10292,13 @@
         <v>101.96</v>
       </c>
       <c r="H178" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I178" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J178" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="N178">
         <v>108.193</v>
@@ -10320,7 +10327,7 @@
     </row>
     <row r="179" spans="2:30">
       <c r="B179" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C179">
         <v>29.39</v>
@@ -10329,13 +10336,13 @@
         <v>101.96</v>
       </c>
       <c r="H179" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I179" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J179" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="N179">
         <v>76.827</v>
@@ -10364,7 +10371,7 @@
     </row>
     <row r="180" spans="2:30">
       <c r="B180" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C180">
         <v>29.39</v>
@@ -10373,13 +10380,13 @@
         <v>101.96</v>
       </c>
       <c r="H180" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I180" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="J180" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="N180">
         <v>37.775</v>
@@ -10408,7 +10415,7 @@
     </row>
     <row r="181" spans="2:30">
       <c r="B181" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C181">
         <v>29.39</v>
@@ -10417,13 +10424,13 @@
         <v>101.96</v>
       </c>
       <c r="H181" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I181" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J181" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="N181">
         <v>102.324</v>
@@ -10452,7 +10459,7 @@
     </row>
     <row r="182" spans="2:30">
       <c r="B182" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C182">
         <v>29.39</v>
@@ -10461,13 +10468,13 @@
         <v>101.96</v>
       </c>
       <c r="H182" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I182" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="J182" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N182">
         <v>90.949</v>
@@ -10496,7 +10503,7 @@
     </row>
     <row r="183" spans="2:30">
       <c r="B183" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C183">
         <v>29.95</v>
@@ -10505,13 +10512,13 @@
         <v>101.96</v>
       </c>
       <c r="H183" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I183" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="J183" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N183">
         <v>396.79</v>
@@ -10540,7 +10547,7 @@
     </row>
     <row r="184" spans="2:30">
       <c r="B184" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C184">
         <v>29.95</v>
@@ -10549,13 +10556,13 @@
         <v>101.96</v>
       </c>
       <c r="H184" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I184" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="J184" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="N184">
         <v>367.22</v>
@@ -10584,7 +10591,7 @@
     </row>
     <row r="185" spans="2:30">
       <c r="B185" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C185">
         <v>29.95</v>
@@ -10593,13 +10600,13 @@
         <v>101.96</v>
       </c>
       <c r="H185" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I185" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="J185" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="N185">
         <v>367.4</v>
@@ -10628,7 +10635,7 @@
     </row>
     <row r="186" spans="2:30">
       <c r="B186" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C186">
         <v>29.95</v>
@@ -10637,13 +10644,13 @@
         <v>101.96</v>
       </c>
       <c r="H186" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I186" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="J186" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="N186">
         <v>349.71</v>
@@ -10672,7 +10679,7 @@
     </row>
     <row r="187" spans="2:30">
       <c r="B187" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C187">
         <v>29.95</v>
@@ -10681,13 +10688,13 @@
         <v>101.96</v>
       </c>
       <c r="H187" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I187" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="J187" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="N187">
         <v>381.816207208</v>
@@ -10716,7 +10723,7 @@
     </row>
     <row r="188" spans="2:30">
       <c r="B188" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C188">
         <v>29.95</v>
@@ -10725,13 +10732,13 @@
         <v>101.96</v>
       </c>
       <c r="H188" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I188" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J188" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="N188">
         <v>346.226290634</v>
@@ -10760,7 +10767,7 @@
     </row>
     <row r="189" spans="2:30">
       <c r="B189" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C189">
         <v>29.95</v>
@@ -10769,13 +10776,13 @@
         <v>101.96</v>
       </c>
       <c r="H189" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I189" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="J189" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="N189">
         <v>314.14046557651</v>
@@ -10804,7 +10811,7 @@
     </row>
     <row r="190" spans="2:30">
       <c r="B190" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C190">
         <v>29.95</v>
@@ -10813,13 +10820,13 @@
         <v>101.96</v>
       </c>
       <c r="H190" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I190" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="J190" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="N190">
         <v>324.841</v>
@@ -10848,7 +10855,7 @@
     </row>
     <row r="191" spans="2:30">
       <c r="B191" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C191">
         <v>29.95</v>
@@ -10857,13 +10864,13 @@
         <v>101.96</v>
       </c>
       <c r="H191" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I191" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="J191" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="N191">
         <v>345.792</v>
@@ -10892,7 +10899,7 @@
     </row>
     <row r="192" spans="2:30">
       <c r="B192" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C192">
         <v>29.95</v>
@@ -10901,13 +10908,13 @@
         <v>101.96</v>
       </c>
       <c r="H192" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I192" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J192" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N192">
         <v>343.444</v>
@@ -10936,7 +10943,7 @@
     </row>
     <row r="193" spans="2:30">
       <c r="B193" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C193">
         <v>29.95</v>
@@ -10945,13 +10952,13 @@
         <v>101.96</v>
       </c>
       <c r="H193" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I193" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="J193" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="N193">
         <v>319.744</v>
@@ -10980,7 +10987,7 @@
     </row>
     <row r="194" spans="2:30">
       <c r="B194" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C194">
         <v>29.95</v>
@@ -10989,13 +10996,13 @@
         <v>101.96</v>
       </c>
       <c r="H194" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I194" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="J194" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="N194">
         <v>337</v>
@@ -11024,7 +11031,7 @@
     </row>
     <row r="195" spans="2:30">
       <c r="B195" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C195">
         <v>29.95</v>
@@ -11033,13 +11040,13 @@
         <v>101.96</v>
       </c>
       <c r="H195" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I195" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="J195" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="N195">
         <v>303.414</v>
@@ -11068,7 +11075,7 @@
     </row>
     <row r="196" spans="2:30">
       <c r="B196" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C196">
         <v>29.95</v>
@@ -11077,13 +11084,13 @@
         <v>101.96</v>
       </c>
       <c r="H196" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I196" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J196" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="N196">
         <v>337.248</v>
@@ -11112,7 +11119,7 @@
     </row>
     <row r="197" spans="2:30">
       <c r="B197" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C197">
         <v>29.95</v>
@@ -11121,13 +11128,13 @@
         <v>101.96</v>
       </c>
       <c r="H197" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I197" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="J197" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N197">
         <v>316.803</v>
@@ -11156,7 +11163,7 @@
     </row>
     <row r="198" spans="2:30">
       <c r="B198" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C198">
         <v>29.95</v>
@@ -11165,13 +11172,13 @@
         <v>101.96</v>
       </c>
       <c r="H198" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I198" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J198" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="N198">
         <v>314.231</v>
@@ -11200,7 +11207,7 @@
     </row>
     <row r="199" spans="2:30">
       <c r="B199" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C199">
         <v>29.95</v>
@@ -11209,13 +11216,13 @@
         <v>101.96</v>
       </c>
       <c r="H199" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I199" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="J199" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="N199">
         <v>326.368</v>
@@ -11244,7 +11251,7 @@
     </row>
     <row r="200" spans="2:30">
       <c r="B200" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C200">
         <v>29.96</v>
@@ -11253,13 +11260,13 @@
         <v>101.96</v>
       </c>
       <c r="H200" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I200" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J200" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="N200">
         <v>958.228</v>
@@ -11288,7 +11295,7 @@
     </row>
     <row r="201" spans="2:30">
       <c r="B201" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C201">
         <v>29.59</v>
@@ -11297,13 +11304,13 @@
         <v>102.03</v>
       </c>
       <c r="H201" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I201" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="J201" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="N201">
         <v>154.11</v>
@@ -11332,7 +11339,7 @@
     </row>
     <row r="202" spans="2:30">
       <c r="B202" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C202">
         <v>29.59</v>
@@ -11341,13 +11348,13 @@
         <v>102.03</v>
       </c>
       <c r="H202" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I202" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="J202" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="N202">
         <v>156.498</v>
@@ -11376,7 +11383,7 @@
     </row>
     <row r="203" spans="2:30">
       <c r="B203" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C203">
         <v>29.59</v>
@@ -11385,13 +11392,13 @@
         <v>102.03</v>
       </c>
       <c r="H203" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I203" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="J203" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="N203">
         <v>153.02</v>
@@ -11420,7 +11427,7 @@
     </row>
     <row r="204" spans="2:30">
       <c r="B204" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C204">
         <v>29.59</v>
@@ -11429,13 +11436,13 @@
         <v>102.03</v>
       </c>
       <c r="H204" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I204" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="J204" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="N204">
         <v>150.44</v>
@@ -11464,7 +11471,7 @@
     </row>
     <row r="205" spans="2:30">
       <c r="B205" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C205">
         <v>29.59</v>
@@ -11473,13 +11480,13 @@
         <v>102.03</v>
       </c>
       <c r="H205" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I205" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="J205" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="N205">
         <v>132.20865636</v>
@@ -11508,7 +11515,7 @@
     </row>
     <row r="206" spans="2:30">
       <c r="B206" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C206">
         <v>29.59</v>
@@ -11517,13 +11524,13 @@
         <v>102.03</v>
       </c>
       <c r="H206" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I206" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="J206" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="N206">
         <v>186.929515528</v>
@@ -11552,7 +11559,7 @@
     </row>
     <row r="207" spans="2:30">
       <c r="B207" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C207">
         <v>29.59</v>
@@ -11561,13 +11568,13 @@
         <v>102.03</v>
       </c>
       <c r="H207" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I207" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="J207" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="N207">
         <v>136.481863193713</v>
@@ -11596,7 +11603,7 @@
     </row>
     <row r="208" spans="2:30">
       <c r="B208" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C208">
         <v>29.59</v>
@@ -11605,13 +11612,13 @@
         <v>102.03</v>
       </c>
       <c r="H208" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I208" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="J208" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="N208">
         <v>189.06</v>
@@ -11640,7 +11647,7 @@
     </row>
     <row r="209" spans="2:30">
       <c r="B209" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C209">
         <v>29.59</v>
@@ -11649,13 +11656,13 @@
         <v>102.03</v>
       </c>
       <c r="H209" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I209" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="J209" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="N209">
         <v>123.358</v>
@@ -11684,7 +11691,7 @@
     </row>
     <row r="210" spans="2:30">
       <c r="B210" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C210">
         <v>29.59</v>
@@ -11693,13 +11700,13 @@
         <v>102.03</v>
       </c>
       <c r="H210" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="I210" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="J210" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="N210">
         <v>202.363</v>
@@ -11728,7 +11735,7 @@
     </row>
     <row r="211" spans="2:30">
       <c r="B211" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C211">
         <v>29.59</v>
@@ -11737,13 +11744,13 @@
         <v>102.03</v>
       </c>
       <c r="H211" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I211" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="J211" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="N211">
         <v>136.444</v>
@@ -11772,7 +11779,7 @@
     </row>
     <row r="212" spans="2:30">
       <c r="B212" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C212">
         <v>29.59</v>
@@ -11781,13 +11788,13 @@
         <v>102.03</v>
       </c>
       <c r="H212" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I212" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="J212" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N212">
         <v>191.47</v>
@@ -11816,7 +11823,7 @@
     </row>
     <row r="213" spans="2:30">
       <c r="B213" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C213">
         <v>29.59</v>
@@ -11825,13 +11832,13 @@
         <v>102.03</v>
       </c>
       <c r="H213" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I213" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="J213" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="N213">
         <v>172.004</v>
@@ -11860,7 +11867,7 @@
     </row>
     <row r="214" spans="2:30">
       <c r="B214" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C214">
         <v>29.59</v>
@@ -11869,13 +11876,13 @@
         <v>102.03</v>
       </c>
       <c r="H214" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I214" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="J214" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N214">
         <v>102.585</v>
@@ -11904,7 +11911,7 @@
     </row>
     <row r="215" spans="2:30">
       <c r="B215" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C215">
         <v>29.59</v>
@@ -11913,13 +11920,13 @@
         <v>102.03</v>
       </c>
       <c r="H215" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I215" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="J215" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="N215">
         <v>167.188</v>
@@ -11948,7 +11955,7 @@
     </row>
     <row r="216" spans="2:30">
       <c r="B216" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C216">
         <v>29.75</v>
@@ -11957,13 +11964,13 @@
         <v>102.06</v>
       </c>
       <c r="H216" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I216" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="J216" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N216">
         <v>422.66</v>
@@ -11992,7 +11999,7 @@
     </row>
     <row r="217" spans="2:30">
       <c r="B217" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C217">
         <v>29.75</v>
@@ -12001,13 +12008,13 @@
         <v>102.06</v>
       </c>
       <c r="H217" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I217" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="J217" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N217">
         <v>365.035</v>
@@ -12036,7 +12043,7 @@
     </row>
     <row r="218" spans="2:30">
       <c r="B218" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C218">
         <v>29.75</v>
@@ -12045,13 +12052,13 @@
         <v>102.06</v>
       </c>
       <c r="H218" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I218" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="J218" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="N218">
         <v>360.63</v>
@@ -12080,7 +12087,7 @@
     </row>
     <row r="219" spans="2:30">
       <c r="B219" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C219">
         <v>29.75</v>
@@ -12089,13 +12096,13 @@
         <v>102.06</v>
       </c>
       <c r="H219" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I219" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="J219" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="N219">
         <v>303.1</v>
@@ -12124,7 +12131,7 @@
     </row>
     <row r="220" spans="2:30">
       <c r="B220" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C220">
         <v>29.75</v>
@@ -12133,13 +12140,13 @@
         <v>102.06</v>
       </c>
       <c r="H220" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I220" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="J220" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="N220">
         <v>250.051349625</v>
@@ -12168,7 +12175,7 @@
     </row>
     <row r="221" spans="2:30">
       <c r="B221" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C221">
         <v>29.75</v>
@@ -12177,13 +12184,13 @@
         <v>102.06</v>
       </c>
       <c r="H221" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I221" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="J221" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N221">
         <v>281.241537682</v>
@@ -12212,7 +12219,7 @@
     </row>
     <row r="222" spans="2:30">
       <c r="B222" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C222">
         <v>29.75</v>
@@ -12221,13 +12228,13 @@
         <v>102.06</v>
       </c>
       <c r="H222" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I222" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="J222" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="N222">
         <v>277.969045210475</v>
@@ -12256,7 +12263,7 @@
     </row>
     <row r="223" spans="2:30">
       <c r="B223" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C223">
         <v>29.75</v>
@@ -12265,13 +12272,13 @@
         <v>102.06</v>
       </c>
       <c r="H223" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I223" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="J223" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="N223">
         <v>295.059</v>
@@ -12300,7 +12307,7 @@
     </row>
     <row r="224" spans="2:30">
       <c r="B224" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C224">
         <v>29.75</v>
@@ -12309,13 +12316,13 @@
         <v>102.06</v>
       </c>
       <c r="H224" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I224" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="J224" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="N224">
         <v>308.06</v>
@@ -12344,7 +12351,7 @@
     </row>
     <row r="225" spans="2:30">
       <c r="B225" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C225">
         <v>29.75</v>
@@ -12353,13 +12360,13 @@
         <v>102.06</v>
       </c>
       <c r="H225" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I225" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="J225" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="N225">
         <v>310.76</v>
@@ -12388,7 +12395,7 @@
     </row>
     <row r="226" spans="2:30">
       <c r="B226" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C226">
         <v>29.75</v>
@@ -12397,13 +12404,13 @@
         <v>102.06</v>
       </c>
       <c r="H226" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I226" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="J226" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="N226">
         <v>320.218</v>
@@ -12432,7 +12439,7 @@
     </row>
     <row r="227" spans="2:30">
       <c r="B227" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C227">
         <v>29.75</v>
@@ -12441,13 +12448,13 @@
         <v>102.06</v>
       </c>
       <c r="H227" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I227" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="J227" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="N227">
         <v>310.937</v>
@@ -12476,7 +12483,7 @@
     </row>
     <row r="228" spans="2:30">
       <c r="B228" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C228">
         <v>29.75</v>
@@ -12485,13 +12492,13 @@
         <v>102.06</v>
       </c>
       <c r="H228" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="I228" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J228" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="N228">
         <v>343.27</v>
@@ -12520,7 +12527,7 @@
     </row>
     <row r="229" spans="2:30">
       <c r="B229" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C229">
         <v>29.75</v>
@@ -12529,13 +12536,13 @@
         <v>102.06</v>
       </c>
       <c r="H229" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I229" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="J229" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="N229">
         <v>334.269</v>
@@ -12564,7 +12571,7 @@
     </row>
     <row r="230" spans="2:30">
       <c r="B230" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C230">
         <v>29.75</v>
@@ -12573,13 +12580,13 @@
         <v>102.06</v>
       </c>
       <c r="H230" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I230" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="J230" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N230">
         <v>304.194</v>
@@ -12608,7 +12615,7 @@
     </row>
     <row r="231" spans="2:30">
       <c r="B231" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C231">
         <v>29.39</v>
@@ -12617,13 +12624,13 @@
         <v>102.1</v>
       </c>
       <c r="H231" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I231" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="J231" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="N231">
         <v>48.74</v>
@@ -12652,7 +12659,7 @@
     </row>
     <row r="232" spans="2:30">
       <c r="B232" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C232">
         <v>29.39</v>
@@ -12661,13 +12668,13 @@
         <v>102.1</v>
       </c>
       <c r="H232" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I232" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="J232" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="N232">
         <v>46.19</v>
@@ -12696,7 +12703,7 @@
     </row>
     <row r="233" spans="2:30">
       <c r="B233" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C233">
         <v>29.39</v>
@@ -12705,13 +12712,13 @@
         <v>102.1</v>
       </c>
       <c r="H233" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I233" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="J233" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="N233">
         <v>46.29</v>
@@ -12740,7 +12747,7 @@
     </row>
     <row r="234" spans="2:30">
       <c r="B234" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C234">
         <v>29.39</v>
@@ -12749,13 +12756,13 @@
         <v>102.1</v>
       </c>
       <c r="H234" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I234" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="J234" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N234">
         <v>49.466434104</v>
@@ -12784,7 +12791,7 @@
     </row>
     <row r="235" spans="2:30">
       <c r="B235" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C235">
         <v>29.39</v>
@@ -12793,13 +12800,13 @@
         <v>102.1</v>
       </c>
       <c r="H235" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I235" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="J235" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="N235">
         <v>47.794226816</v>
@@ -12828,7 +12835,7 @@
     </row>
     <row r="236" spans="2:30">
       <c r="B236" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C236">
         <v>29.39</v>
@@ -12837,13 +12844,13 @@
         <v>102.1</v>
       </c>
       <c r="H236" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I236" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="J236" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="N236">
         <v>48.773</v>
@@ -12872,7 +12879,7 @@
     </row>
     <row r="237" spans="2:30">
       <c r="B237" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C237">
         <v>29.39</v>
@@ -12881,13 +12888,13 @@
         <v>102.1</v>
       </c>
       <c r="H237" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I237" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="J237" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="N237">
         <v>58.763</v>
@@ -12916,7 +12923,7 @@
     </row>
     <row r="238" spans="2:30">
       <c r="B238" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C238">
         <v>29.39</v>
@@ -12925,13 +12932,13 @@
         <v>102.1</v>
       </c>
       <c r="H238" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I238" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="J238" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="N238">
         <v>45.53899999999999</v>
@@ -12960,7 +12967,7 @@
     </row>
     <row r="239" spans="2:30">
       <c r="B239" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C239">
         <v>29.39</v>
@@ -12969,13 +12976,13 @@
         <v>102.1</v>
       </c>
       <c r="H239" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I239" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="J239" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="N239">
         <v>47.249</v>
@@ -13004,7 +13011,7 @@
     </row>
     <row r="240" spans="2:30">
       <c r="B240" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C240">
         <v>29.62</v>
@@ -13013,13 +13020,13 @@
         <v>102.11</v>
       </c>
       <c r="H240" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="I240" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="J240" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="N240">
         <v>108.43</v>
@@ -13048,7 +13055,7 @@
     </row>
     <row r="241" spans="2:30">
       <c r="B241" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C241">
         <v>29.62</v>
@@ -13057,13 +13064,13 @@
         <v>102.11</v>
       </c>
       <c r="H241" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="I241" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="J241" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="N241">
         <v>106.532</v>
@@ -13092,7 +13099,7 @@
     </row>
     <row r="242" spans="2:30">
       <c r="B242" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C242">
         <v>29.62</v>
@@ -13101,13 +13108,13 @@
         <v>102.11</v>
       </c>
       <c r="H242" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I242" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="J242" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="N242">
         <v>107.62</v>
@@ -13136,7 +13143,7 @@
     </row>
     <row r="243" spans="2:30">
       <c r="B243" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C243">
         <v>29.62</v>
@@ -13145,13 +13152,13 @@
         <v>102.11</v>
       </c>
       <c r="H243" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I243" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="J243" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="N243">
         <v>111.76</v>
@@ -13180,7 +13187,7 @@
     </row>
     <row r="244" spans="2:30">
       <c r="B244" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C244">
         <v>29.62</v>
@@ -13189,13 +13196,13 @@
         <v>102.11</v>
       </c>
       <c r="H244" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I244" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="J244" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="N244">
         <v>111.677460768</v>
@@ -13224,7 +13231,7 @@
     </row>
     <row r="245" spans="2:30">
       <c r="B245" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C245">
         <v>29.62</v>
@@ -13233,13 +13240,13 @@
         <v>102.11</v>
       </c>
       <c r="H245" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I245" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="J245" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="N245">
         <v>92.700091008</v>
@@ -13268,7 +13275,7 @@
     </row>
     <row r="246" spans="2:30">
       <c r="B246" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C246">
         <v>29.62</v>
@@ -13277,13 +13284,13 @@
         <v>102.11</v>
       </c>
       <c r="H246" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I246" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="J246" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="N246">
         <v>78.57781268330039</v>
@@ -13312,7 +13319,7 @@
     </row>
     <row r="247" spans="2:30">
       <c r="B247" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C247">
         <v>29.62</v>
@@ -13321,13 +13328,13 @@
         <v>102.11</v>
       </c>
       <c r="H247" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I247" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="J247" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="N247">
         <v>82.334</v>
@@ -13356,7 +13363,7 @@
     </row>
     <row r="248" spans="2:30">
       <c r="B248" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C248">
         <v>29.62</v>
@@ -13365,13 +13372,13 @@
         <v>102.11</v>
       </c>
       <c r="H248" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I248" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="J248" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="N248">
         <v>84.38200000000001</v>
@@ -13400,7 +13407,7 @@
     </row>
     <row r="249" spans="2:30">
       <c r="B249" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C249">
         <v>29.62</v>
@@ -13409,13 +13416,13 @@
         <v>102.11</v>
       </c>
       <c r="H249" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I249" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="J249" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="N249">
         <v>96.627</v>
@@ -13444,7 +13451,7 @@
     </row>
     <row r="250" spans="2:30">
       <c r="B250" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C250">
         <v>29.62</v>
@@ -13453,13 +13460,13 @@
         <v>102.11</v>
       </c>
       <c r="H250" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I250" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="J250" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="N250">
         <v>94.995</v>
@@ -13488,7 +13495,7 @@
     </row>
     <row r="251" spans="2:30">
       <c r="B251" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C251">
         <v>29.62</v>
@@ -13497,13 +13504,13 @@
         <v>102.11</v>
       </c>
       <c r="H251" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I251" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="J251" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N251">
         <v>77.114</v>
@@ -13532,7 +13539,7 @@
     </row>
     <row r="252" spans="2:30">
       <c r="B252" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C252">
         <v>29.62</v>
@@ -13541,13 +13548,13 @@
         <v>102.11</v>
       </c>
       <c r="H252" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I252" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="J252" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="N252">
         <v>119.628</v>
@@ -13576,7 +13583,7 @@
     </row>
     <row r="253" spans="2:30">
       <c r="B253" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C253">
         <v>29.62</v>
@@ -13585,13 +13592,13 @@
         <v>102.11</v>
       </c>
       <c r="H253" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I253" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J253" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N253">
         <v>117.666</v>
@@ -13620,7 +13627,7 @@
     </row>
     <row r="254" spans="2:30">
       <c r="B254" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C254">
         <v>29.54</v>
@@ -13629,13 +13636,13 @@
         <v>102.14</v>
       </c>
       <c r="H254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I254" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="J254" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N254">
         <v>326.227</v>
@@ -13664,7 +13671,7 @@
     </row>
     <row r="255" spans="2:30">
       <c r="B255" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C255">
         <v>29.54</v>
@@ -13673,13 +13680,13 @@
         <v>102.14</v>
       </c>
       <c r="H255" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I255" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="J255" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="N255">
         <v>334.526</v>
@@ -13708,7 +13715,7 @@
     </row>
     <row r="256" spans="2:30">
       <c r="B256" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C256">
         <v>29.54</v>
@@ -13717,13 +13724,13 @@
         <v>102.14</v>
       </c>
       <c r="H256" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="I256" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="J256" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="N256">
         <v>328.381</v>
@@ -13752,7 +13759,7 @@
     </row>
     <row r="257" spans="2:30">
       <c r="B257" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C257">
         <v>29.54</v>
@@ -13761,13 +13768,13 @@
         <v>102.14</v>
       </c>
       <c r="H257" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I257" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J257" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="N257">
         <v>351.15</v>
@@ -13796,7 +13803,7 @@
     </row>
     <row r="258" spans="2:30">
       <c r="B258" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C258">
         <v>29.54</v>
@@ -13805,13 +13812,13 @@
         <v>102.14</v>
       </c>
       <c r="H258" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I258" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="J258" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N258">
         <v>322.656</v>
@@ -13840,7 +13847,7 @@
     </row>
     <row r="259" spans="2:30">
       <c r="B259" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C259">
         <v>29.54</v>
@@ -13849,13 +13856,13 @@
         <v>102.14</v>
       </c>
       <c r="H259" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I259" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="J259" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="N259">
         <v>302.997</v>
@@ -13884,7 +13891,7 @@
     </row>
     <row r="260" spans="2:30">
       <c r="B260" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C260">
         <v>29.49</v>
@@ -13893,13 +13900,13 @@
         <v>102.14</v>
       </c>
       <c r="H260" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I260" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="J260" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="N260">
         <v>76.93000000000001</v>
@@ -13928,7 +13935,7 @@
     </row>
     <row r="261" spans="2:30">
       <c r="B261" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C261">
         <v>29.49</v>
@@ -13937,13 +13944,13 @@
         <v>102.14</v>
       </c>
       <c r="H261" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I261" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="J261" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="N261">
         <v>73.37</v>
@@ -13972,7 +13979,7 @@
     </row>
     <row r="262" spans="2:30">
       <c r="B262" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C262">
         <v>29.49</v>
@@ -13981,13 +13988,13 @@
         <v>102.14</v>
       </c>
       <c r="H262" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I262" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="J262" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="N262">
         <v>79.12</v>
@@ -14016,7 +14023,7 @@
     </row>
     <row r="263" spans="2:30">
       <c r="B263" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C263">
         <v>29.49</v>
@@ -14025,13 +14032,13 @@
         <v>102.14</v>
       </c>
       <c r="H263" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I263" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="J263" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="N263">
         <v>79.11</v>
@@ -14060,7 +14067,7 @@
     </row>
     <row r="264" spans="2:30">
       <c r="B264" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C264">
         <v>29.49</v>
@@ -14069,13 +14076,13 @@
         <v>102.14</v>
       </c>
       <c r="H264" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I264" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="J264" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="N264">
         <v>86.326364056</v>
@@ -14104,7 +14111,7 @@
     </row>
     <row r="265" spans="2:30">
       <c r="B265" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C265">
         <v>29.49</v>
@@ -14113,13 +14120,13 @@
         <v>102.14</v>
       </c>
       <c r="H265" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I265" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="J265" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N265">
         <v>79.875318166</v>
@@ -14148,7 +14155,7 @@
     </row>
     <row r="266" spans="2:30">
       <c r="B266" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C266">
         <v>29.49</v>
@@ -14157,13 +14164,13 @@
         <v>102.14</v>
       </c>
       <c r="H266" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I266" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="J266" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="N266">
         <v>80.6236034880382</v>
@@ -14192,7 +14199,7 @@
     </row>
     <row r="267" spans="2:30">
       <c r="B267" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C267">
         <v>29.49</v>
@@ -14201,13 +14208,13 @@
         <v>102.14</v>
       </c>
       <c r="H267" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I267" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J267" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N267">
         <v>87.71699999999998</v>
@@ -14236,7 +14243,7 @@
     </row>
     <row r="268" spans="2:30">
       <c r="B268" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C268">
         <v>29.49</v>
@@ -14245,13 +14252,13 @@
         <v>102.14</v>
       </c>
       <c r="H268" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I268" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="J268" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="N268">
         <v>73.208</v>
@@ -14280,7 +14287,7 @@
     </row>
     <row r="269" spans="2:30">
       <c r="B269" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C269">
         <v>29.49</v>
@@ -14289,13 +14296,13 @@
         <v>102.14</v>
       </c>
       <c r="H269" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="I269" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="J269" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="N269">
         <v>115.402</v>
@@ -14324,7 +14331,7 @@
     </row>
     <row r="270" spans="2:30">
       <c r="B270" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C270">
         <v>29.44</v>
@@ -14333,13 +14340,13 @@
         <v>102.22</v>
       </c>
       <c r="H270" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I270" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="J270" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="N270">
         <v>38.6</v>
@@ -14368,7 +14375,7 @@
     </row>
     <row r="271" spans="2:30">
       <c r="B271" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C271">
         <v>29.44</v>
@@ -14377,13 +14384,13 @@
         <v>102.22</v>
       </c>
       <c r="H271" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I271" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="J271" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="N271">
         <v>37.61</v>
@@ -14412,7 +14419,7 @@
     </row>
     <row r="272" spans="2:30">
       <c r="B272" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C272">
         <v>29.44</v>
@@ -14421,13 +14428,13 @@
         <v>102.22</v>
       </c>
       <c r="H272" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="I272" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="J272" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="N272">
         <v>35.14</v>
@@ -14456,7 +14463,7 @@
     </row>
     <row r="273" spans="2:30">
       <c r="B273" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C273">
         <v>29.44</v>
@@ -14465,13 +14472,13 @@
         <v>102.22</v>
       </c>
       <c r="H273" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="I273" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="J273" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N273">
         <v>36.487003296</v>
@@ -14500,7 +14507,7 @@
     </row>
     <row r="274" spans="2:30">
       <c r="B274" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C274">
         <v>29.44</v>
@@ -14509,13 +14516,13 @@
         <v>102.22</v>
       </c>
       <c r="H274" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="I274" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="J274" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="N274">
         <v>34.978820716</v>
@@ -14544,7 +14551,7 @@
     </row>
     <row r="275" spans="2:30">
       <c r="B275" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C275">
         <v>29.44</v>
@@ -14553,13 +14560,13 @@
         <v>102.22</v>
       </c>
       <c r="H275" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I275" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="J275" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="N275">
         <v>35.8596279774078</v>
@@ -14588,7 +14595,7 @@
     </row>
     <row r="276" spans="2:30">
       <c r="B276" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C276">
         <v>29.44</v>
@@ -14597,13 +14604,13 @@
         <v>102.22</v>
       </c>
       <c r="H276" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I276" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="J276" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="N276">
         <v>35.25</v>
@@ -14632,7 +14639,7 @@
     </row>
     <row r="277" spans="2:30">
       <c r="B277" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C277">
         <v>29.44</v>
@@ -14641,13 +14648,13 @@
         <v>102.22</v>
       </c>
       <c r="H277" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I277" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="J277" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="N277">
         <v>35.289</v>
@@ -14676,7 +14683,7 @@
     </row>
     <row r="278" spans="2:30">
       <c r="B278" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C278">
         <v>29.44</v>
@@ -14685,13 +14692,13 @@
         <v>102.22</v>
       </c>
       <c r="H278" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I278" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="J278" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="N278">
         <v>33.985</v>
@@ -14720,7 +14727,7 @@
     </row>
     <row r="279" spans="2:30">
       <c r="B279" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C279">
         <v>29.44</v>
@@ -14729,13 +14736,13 @@
         <v>102.22</v>
       </c>
       <c r="H279" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I279" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="J279" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="N279">
         <v>35.828</v>
@@ -14764,7 +14771,7 @@
     </row>
     <row r="280" spans="2:30">
       <c r="B280" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C280">
         <v>29.44</v>
@@ -14773,13 +14780,13 @@
         <v>102.22</v>
       </c>
       <c r="H280" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I280" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="J280" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="N280">
         <v>36.786</v>

--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/MDPI-Xianshuihe_Datenbank/before_conversion_xian_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/MDPI-Xianshuihe_Datenbank/before_conversion_xian_mapped_readable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1178" uniqueCount="682">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1458" uniqueCount="683">
   <si>
     <t>location</t>
   </si>
@@ -239,6 +239,9 @@
   </si>
   <si>
     <t>W43</t>
+  </si>
+  <si>
+    <t>Metamorphic Rock</t>
   </si>
   <si>
     <t>10</t>
@@ -2423,7 +2426,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE280"/>
+  <dimension ref="A1:AE281"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -2431,7 +2434,7 @@
     <col min="3" max="3" width="16.7109375" customWidth="1"/>
     <col min="4" max="4" width="17.7109375" customWidth="1"/>
     <col min="5" max="5" width="16.7109375" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" customWidth="1"/>
     <col min="7" max="7" width="22.7109375" customWidth="1"/>
     <col min="8" max="8" width="18.7109375" customWidth="1"/>
     <col min="9" max="9" width="38.7109375" customWidth="1"/>
@@ -2562,14 +2565,17 @@
       <c r="D2">
         <v>100.25</v>
       </c>
+      <c r="F2" t="s">
+        <v>75</v>
+      </c>
       <c r="H2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="J2" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N2">
         <v>68.41</v>
@@ -2606,14 +2612,17 @@
       <c r="D3">
         <v>100.25</v>
       </c>
+      <c r="F3" t="s">
+        <v>75</v>
+      </c>
       <c r="H3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="J3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="N3">
         <v>83.405</v>
@@ -2650,14 +2659,17 @@
       <c r="D4">
         <v>100.25</v>
       </c>
+      <c r="F4" t="s">
+        <v>75</v>
+      </c>
       <c r="H4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J4" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N4">
         <v>68.04000000000001</v>
@@ -2694,14 +2706,17 @@
       <c r="D5">
         <v>100.29</v>
       </c>
+      <c r="F5" t="s">
+        <v>75</v>
+      </c>
       <c r="H5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I5" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="J5" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="N5">
         <v>2.749</v>
@@ -2738,14 +2753,17 @@
       <c r="D6">
         <v>100.43</v>
       </c>
+      <c r="F6" t="s">
+        <v>75</v>
+      </c>
       <c r="H6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="J6" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N6">
         <v>13.495</v>
@@ -2776,14 +2794,17 @@
       <c r="B7" t="s">
         <v>34</v>
       </c>
+      <c r="F7" t="s">
+        <v>75</v>
+      </c>
       <c r="H7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I7" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J7" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="N7">
         <v>15.472</v>
@@ -2820,14 +2841,17 @@
       <c r="D8">
         <v>100.46</v>
       </c>
+      <c r="F8" t="s">
+        <v>75</v>
+      </c>
       <c r="H8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J8" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N8">
         <v>448.78</v>
@@ -2864,14 +2888,17 @@
       <c r="D9">
         <v>100.46</v>
       </c>
+      <c r="F9" t="s">
+        <v>75</v>
+      </c>
       <c r="H9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="J9" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="N9">
         <v>433.504</v>
@@ -2908,14 +2935,17 @@
       <c r="D10">
         <v>100.46</v>
       </c>
+      <c r="F10" t="s">
+        <v>75</v>
+      </c>
       <c r="H10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="J10" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="N10">
         <v>449.124</v>
@@ -2952,14 +2982,17 @@
       <c r="D11">
         <v>100.72</v>
       </c>
+      <c r="F11" t="s">
+        <v>75</v>
+      </c>
       <c r="H11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I11" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="J11" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="N11">
         <v>306.745</v>
@@ -2996,14 +3029,17 @@
       <c r="D12">
         <v>100.72</v>
       </c>
+      <c r="F12" t="s">
+        <v>75</v>
+      </c>
       <c r="H12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J12" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N12">
         <v>372.217</v>
@@ -3040,14 +3076,17 @@
       <c r="D13">
         <v>100.8</v>
       </c>
+      <c r="F13" t="s">
+        <v>75</v>
+      </c>
       <c r="H13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I13" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="J13" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N13">
         <v>607.0700000000001</v>
@@ -3084,14 +3123,17 @@
       <c r="D14">
         <v>100.8</v>
       </c>
+      <c r="F14" t="s">
+        <v>75</v>
+      </c>
       <c r="H14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I14" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="J14" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N14">
         <v>619.72</v>
@@ -3128,14 +3170,17 @@
       <c r="D15">
         <v>100.8</v>
       </c>
+      <c r="F15" t="s">
+        <v>75</v>
+      </c>
       <c r="H15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I15" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J15" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="N15">
         <v>593.59</v>
@@ -3172,14 +3217,17 @@
       <c r="D16">
         <v>100.8</v>
       </c>
+      <c r="F16" t="s">
+        <v>75</v>
+      </c>
       <c r="H16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I16" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="J16" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N16">
         <v>619.91</v>
@@ -3216,14 +3264,17 @@
       <c r="D17">
         <v>100.8</v>
       </c>
+      <c r="F17" t="s">
+        <v>75</v>
+      </c>
       <c r="H17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I17" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="J17" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="N17">
         <v>876.182922395</v>
@@ -3257,14 +3308,17 @@
       <c r="D18">
         <v>100.8</v>
       </c>
+      <c r="F18" t="s">
+        <v>75</v>
+      </c>
       <c r="H18" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I18" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="J18" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N18">
         <v>618.240735924</v>
@@ -3301,14 +3355,17 @@
       <c r="D19">
         <v>100.8</v>
       </c>
+      <c r="F19" t="s">
+        <v>75</v>
+      </c>
       <c r="H19" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I19" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J19" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N19">
         <v>660.0062804354829</v>
@@ -3345,14 +3402,17 @@
       <c r="D20">
         <v>100.9</v>
       </c>
+      <c r="F20" t="s">
+        <v>75</v>
+      </c>
       <c r="H20" t="s">
+        <v>94</v>
+      </c>
+      <c r="I20" t="s">
         <v>93</v>
       </c>
-      <c r="I20" t="s">
-        <v>92</v>
-      </c>
       <c r="J20" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="N20">
         <v>402.443</v>
@@ -3389,14 +3449,17 @@
       <c r="D21">
         <v>100.9</v>
       </c>
+      <c r="F21" t="s">
+        <v>75</v>
+      </c>
       <c r="H21" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I21" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="J21" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N21">
         <v>396.857</v>
@@ -3433,14 +3496,17 @@
       <c r="D22">
         <v>100.92</v>
       </c>
+      <c r="F22" t="s">
+        <v>75</v>
+      </c>
       <c r="H22" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I22" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="J22" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="N22">
         <v>301.027</v>
@@ -3477,14 +3543,17 @@
       <c r="D23">
         <v>100.92</v>
       </c>
+      <c r="F23" t="s">
+        <v>75</v>
+      </c>
       <c r="H23" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I23" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J23" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N23">
         <v>295.613</v>
@@ -3521,14 +3590,17 @@
       <c r="D24">
         <v>100.92</v>
       </c>
+      <c r="F24" t="s">
+        <v>75</v>
+      </c>
       <c r="H24" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I24" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="J24" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N24">
         <v>287.125</v>
@@ -3565,14 +3637,17 @@
       <c r="D25">
         <v>100.92</v>
       </c>
+      <c r="F25" t="s">
+        <v>75</v>
+      </c>
       <c r="H25" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I25" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="J25" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="N25">
         <v>270.155</v>
@@ -3609,14 +3684,17 @@
       <c r="D26">
         <v>101.01</v>
       </c>
+      <c r="F26" t="s">
+        <v>75</v>
+      </c>
       <c r="H26" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I26" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J26" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N26">
         <v>81.69600000000001</v>
@@ -3653,14 +3731,17 @@
       <c r="D27">
         <v>101.01</v>
       </c>
+      <c r="F27" t="s">
+        <v>75</v>
+      </c>
       <c r="H27" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I27" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J27" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N27">
         <v>79.572</v>
@@ -3697,14 +3778,17 @@
       <c r="D28">
         <v>101.01</v>
       </c>
+      <c r="F28" t="s">
+        <v>75</v>
+      </c>
       <c r="H28" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I28" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="J28" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N28">
         <v>77.64</v>
@@ -3741,14 +3825,17 @@
       <c r="D29">
         <v>101.02</v>
       </c>
+      <c r="F29" t="s">
+        <v>75</v>
+      </c>
       <c r="H29" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I29" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="J29" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="N29">
         <v>31.22</v>
@@ -3785,14 +3872,17 @@
       <c r="D30">
         <v>101.08</v>
       </c>
+      <c r="F30" t="s">
+        <v>75</v>
+      </c>
       <c r="H30" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I30" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J30" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N30">
         <v>16.57</v>
@@ -3829,14 +3919,17 @@
       <c r="D31">
         <v>101.08</v>
       </c>
+      <c r="F31" t="s">
+        <v>75</v>
+      </c>
       <c r="H31" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I31" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J31" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N31">
         <v>16.835</v>
@@ -3873,14 +3966,17 @@
       <c r="D32">
         <v>101.08</v>
       </c>
+      <c r="F32" t="s">
+        <v>75</v>
+      </c>
       <c r="H32" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I32" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J32" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N32">
         <v>15.121</v>
@@ -3917,14 +4013,17 @@
       <c r="D33">
         <v>101.1</v>
       </c>
+      <c r="F33" t="s">
+        <v>75</v>
+      </c>
       <c r="H33" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I33" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J33" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="N33">
         <v>494.378215234929</v>
@@ -3961,14 +4060,17 @@
       <c r="D34">
         <v>101.1</v>
       </c>
+      <c r="F34" t="s">
+        <v>75</v>
+      </c>
       <c r="H34" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I34" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="J34" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N34">
         <v>540.4010000000001</v>
@@ -4005,14 +4107,17 @@
       <c r="D35">
         <v>101.1</v>
       </c>
+      <c r="F35" t="s">
+        <v>75</v>
+      </c>
       <c r="H35" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I35" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J35" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N35">
         <v>538.619</v>
@@ -4049,14 +4154,17 @@
       <c r="D36">
         <v>101.1</v>
       </c>
+      <c r="F36" t="s">
+        <v>75</v>
+      </c>
       <c r="H36" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I36" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J36" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N36">
         <v>551.7909999999999</v>
@@ -4093,14 +4201,17 @@
       <c r="D37">
         <v>101.1</v>
       </c>
+      <c r="F37" t="s">
+        <v>75</v>
+      </c>
       <c r="H37" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I37" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="J37" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N37">
         <v>530.293</v>
@@ -4137,14 +4248,17 @@
       <c r="D38">
         <v>101.17</v>
       </c>
+      <c r="F38" t="s">
+        <v>75</v>
+      </c>
       <c r="H38" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I38" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J38" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N38">
         <v>183.560762233806</v>
@@ -4181,14 +4295,17 @@
       <c r="D39">
         <v>101.17</v>
       </c>
+      <c r="F39" t="s">
+        <v>75</v>
+      </c>
       <c r="H39" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I39" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="J39" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="N39">
         <v>189.444</v>
@@ -4225,14 +4342,17 @@
       <c r="D40">
         <v>101.18</v>
       </c>
+      <c r="F40" t="s">
+        <v>75</v>
+      </c>
       <c r="H40" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I40" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="J40" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N40">
         <v>213.264242178457</v>
@@ -4269,14 +4389,17 @@
       <c r="D41">
         <v>101.18</v>
       </c>
+      <c r="F41" t="s">
+        <v>75</v>
+      </c>
       <c r="H41" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I41" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="J41" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N41">
         <v>224.145</v>
@@ -4313,14 +4436,17 @@
       <c r="D42">
         <v>101.18</v>
       </c>
+      <c r="F42" t="s">
+        <v>75</v>
+      </c>
       <c r="H42" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I42" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="J42" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="N42">
         <v>179.533228402099</v>
@@ -4357,14 +4483,17 @@
       <c r="D43">
         <v>101.18</v>
       </c>
+      <c r="F43" t="s">
+        <v>75</v>
+      </c>
       <c r="H43" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I43" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J43" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="N43">
         <v>153.556</v>
@@ -4401,14 +4530,17 @@
       <c r="D44">
         <v>101.24</v>
       </c>
+      <c r="F44" t="s">
+        <v>75</v>
+      </c>
       <c r="H44" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I44" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="J44" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N44">
         <v>854</v>
@@ -4445,14 +4577,17 @@
       <c r="D45">
         <v>101.24</v>
       </c>
+      <c r="F45" t="s">
+        <v>75</v>
+      </c>
       <c r="H45" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I45" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J45" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="N45">
         <v>844.652772026</v>
@@ -4489,14 +4624,17 @@
       <c r="D46">
         <v>101.24</v>
       </c>
+      <c r="F46" t="s">
+        <v>75</v>
+      </c>
       <c r="H46" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I46" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="J46" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="N46">
         <v>845.8969999999999</v>
@@ -4533,14 +4671,17 @@
       <c r="D47">
         <v>101.24</v>
       </c>
+      <c r="F47" t="s">
+        <v>75</v>
+      </c>
       <c r="H47" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I47" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J47" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N47">
         <v>839</v>
@@ -4577,14 +4718,17 @@
       <c r="D48">
         <v>101.24</v>
       </c>
+      <c r="F48" t="s">
+        <v>75</v>
+      </c>
       <c r="H48" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I48" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J48" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N48">
         <v>891.152</v>
@@ -4621,14 +4765,17 @@
       <c r="D49">
         <v>101.24</v>
       </c>
+      <c r="F49" t="s">
+        <v>75</v>
+      </c>
       <c r="H49" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I49" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J49" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="N49">
         <v>859.674</v>
@@ -4665,14 +4812,17 @@
       <c r="D50">
         <v>101.24</v>
       </c>
+      <c r="F50" t="s">
+        <v>75</v>
+      </c>
       <c r="H50" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I50" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="J50" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="N50">
         <v>221.8</v>
@@ -4709,14 +4859,17 @@
       <c r="D51">
         <v>101.24</v>
       </c>
+      <c r="F51" t="s">
+        <v>75</v>
+      </c>
       <c r="H51" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I51" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="J51" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="N51">
         <v>205.03</v>
@@ -4753,14 +4906,17 @@
       <c r="D52">
         <v>101.24</v>
       </c>
+      <c r="F52" t="s">
+        <v>75</v>
+      </c>
       <c r="H52" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I52" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="J52" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="N52">
         <v>198.93</v>
@@ -4797,14 +4953,17 @@
       <c r="D53">
         <v>101.24</v>
       </c>
+      <c r="F53" t="s">
+        <v>75</v>
+      </c>
       <c r="H53" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I53" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="J53" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="N53">
         <v>176.77</v>
@@ -4841,14 +5000,17 @@
       <c r="D54">
         <v>101.24</v>
       </c>
+      <c r="F54" t="s">
+        <v>75</v>
+      </c>
       <c r="H54" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I54" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="J54" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="N54">
         <v>227.774630136</v>
@@ -4885,14 +5047,17 @@
       <c r="D55">
         <v>101.24</v>
       </c>
+      <c r="F55" t="s">
+        <v>75</v>
+      </c>
       <c r="H55" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I55" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J55" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="N55">
         <v>259.59925453</v>
@@ -4929,14 +5094,17 @@
       <c r="D56">
         <v>101.24</v>
       </c>
+      <c r="F56" t="s">
+        <v>75</v>
+      </c>
       <c r="H56" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I56" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J56" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="N56">
         <v>239.722</v>
@@ -4973,14 +5141,17 @@
       <c r="D57">
         <v>101.24</v>
       </c>
+      <c r="F57" t="s">
+        <v>75</v>
+      </c>
       <c r="H57" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I57" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="J57" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N57">
         <v>280.491</v>
@@ -5017,14 +5188,17 @@
       <c r="D58">
         <v>101.24</v>
       </c>
+      <c r="F58" t="s">
+        <v>75</v>
+      </c>
       <c r="H58" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I58" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J58" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="N58">
         <v>266.511</v>
@@ -5061,14 +5235,17 @@
       <c r="D59">
         <v>101.24</v>
       </c>
+      <c r="F59" t="s">
+        <v>75</v>
+      </c>
       <c r="H59" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I59" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="J59" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N59">
         <v>293.866</v>
@@ -5105,14 +5282,17 @@
       <c r="D60">
         <v>101.24</v>
       </c>
+      <c r="F60" t="s">
+        <v>75</v>
+      </c>
       <c r="H60" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I60" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="J60" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N60">
         <v>267.166</v>
@@ -5149,14 +5329,17 @@
       <c r="D61">
         <v>101.24</v>
       </c>
+      <c r="F61" t="s">
+        <v>75</v>
+      </c>
       <c r="H61" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I61" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="J61" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N61">
         <v>310.06</v>
@@ -5193,14 +5376,17 @@
       <c r="D62">
         <v>101.24</v>
       </c>
+      <c r="F62" t="s">
+        <v>75</v>
+      </c>
       <c r="H62" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I62" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="J62" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="N62">
         <v>288.86</v>
@@ -5237,14 +5423,17 @@
       <c r="D63">
         <v>101.24</v>
       </c>
+      <c r="F63" t="s">
+        <v>75</v>
+      </c>
       <c r="H63" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I63" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="J63" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="N63">
         <v>280.27</v>
@@ -5281,14 +5470,17 @@
       <c r="D64">
         <v>101.24</v>
       </c>
+      <c r="F64" t="s">
+        <v>75</v>
+      </c>
       <c r="H64" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I64" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="J64" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N64">
         <v>281.7</v>
@@ -5325,14 +5517,17 @@
       <c r="D65">
         <v>101.24</v>
       </c>
+      <c r="F65" t="s">
+        <v>75</v>
+      </c>
       <c r="H65" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I65" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="J65" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="N65">
         <v>303.453234528</v>
@@ -5369,14 +5564,17 @@
       <c r="D66">
         <v>101.24</v>
       </c>
+      <c r="F66" t="s">
+        <v>75</v>
+      </c>
       <c r="H66" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I66" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="J66" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N66">
         <v>287.306077366</v>
@@ -5413,14 +5611,17 @@
       <c r="D67">
         <v>101.24</v>
       </c>
+      <c r="F67" t="s">
+        <v>75</v>
+      </c>
       <c r="H67" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I67" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="J67" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N67">
         <v>286.169</v>
@@ -5457,14 +5658,17 @@
       <c r="D68">
         <v>101.24</v>
       </c>
+      <c r="F68" t="s">
+        <v>75</v>
+      </c>
       <c r="H68" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I68" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="J68" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="N68">
         <v>295.381</v>
@@ -5501,14 +5705,17 @@
       <c r="D69">
         <v>101.24</v>
       </c>
+      <c r="F69" t="s">
+        <v>75</v>
+      </c>
       <c r="H69" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I69" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J69" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="N69">
         <v>158.977</v>
@@ -5545,14 +5752,17 @@
       <c r="D70">
         <v>101.24</v>
       </c>
+      <c r="F70" t="s">
+        <v>75</v>
+      </c>
       <c r="H70" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I70" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="J70" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N70">
         <v>281.929</v>
@@ -5589,14 +5799,17 @@
       <c r="D71">
         <v>101.24</v>
       </c>
+      <c r="F71" t="s">
+        <v>75</v>
+      </c>
       <c r="H71" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I71" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="J71" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="N71">
         <v>290.776</v>
@@ -5633,14 +5846,17 @@
       <c r="D72">
         <v>101.29</v>
       </c>
+      <c r="F72" t="s">
+        <v>75</v>
+      </c>
       <c r="H72" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I72" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="J72" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="N72">
         <v>112.508882122064</v>
@@ -5677,14 +5893,17 @@
       <c r="D73">
         <v>101.29</v>
       </c>
+      <c r="F73" t="s">
+        <v>75</v>
+      </c>
       <c r="H73" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I73" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="J73" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="N73">
         <v>115.738</v>
@@ -5721,14 +5940,17 @@
       <c r="D74">
         <v>101.29</v>
       </c>
+      <c r="F74" t="s">
+        <v>75</v>
+      </c>
       <c r="H74" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I74" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="J74" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="N74">
         <v>117.333</v>
@@ -5765,14 +5987,17 @@
       <c r="D75">
         <v>101.29</v>
       </c>
+      <c r="F75" t="s">
+        <v>75</v>
+      </c>
       <c r="H75" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I75" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J75" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="N75">
         <v>117.791</v>
@@ -5809,14 +6034,17 @@
       <c r="D76">
         <v>101.29</v>
       </c>
+      <c r="F76" t="s">
+        <v>75</v>
+      </c>
       <c r="H76" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I76" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="J76" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N76">
         <v>114.213</v>
@@ -5853,14 +6081,17 @@
       <c r="D77">
         <v>101.4</v>
       </c>
+      <c r="F77" t="s">
+        <v>75</v>
+      </c>
       <c r="H77" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I77" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="J77" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="N77">
         <v>221.437023331912</v>
@@ -5897,14 +6128,17 @@
       <c r="D78">
         <v>101.53</v>
       </c>
+      <c r="F78" t="s">
+        <v>75</v>
+      </c>
       <c r="H78" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I78" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J78" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N78">
         <v>124.988</v>
@@ -5941,14 +6175,17 @@
       <c r="D79">
         <v>101.53</v>
       </c>
+      <c r="F79" t="s">
+        <v>75</v>
+      </c>
       <c r="H79" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I79" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="J79" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N79">
         <v>118.584</v>
@@ -5985,14 +6222,17 @@
       <c r="D80">
         <v>101.53</v>
       </c>
+      <c r="F80" t="s">
+        <v>75</v>
+      </c>
       <c r="H80" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I80" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="J80" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N80">
         <v>113.311</v>
@@ -6029,14 +6269,17 @@
       <c r="D81">
         <v>101.62</v>
       </c>
+      <c r="F81" t="s">
+        <v>75</v>
+      </c>
       <c r="H81" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I81" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="J81" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N81">
         <v>443</v>
@@ -6073,14 +6316,17 @@
       <c r="D82">
         <v>101.62</v>
       </c>
+      <c r="F82" t="s">
+        <v>75</v>
+      </c>
       <c r="H82" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I82" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="J82" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="N82">
         <v>417.075</v>
@@ -6117,14 +6363,17 @@
       <c r="D83">
         <v>101.62</v>
       </c>
+      <c r="F83" t="s">
+        <v>75</v>
+      </c>
       <c r="H83" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I83" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J83" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N83">
         <v>463.31</v>
@@ -6161,14 +6410,17 @@
       <c r="D84">
         <v>101.62</v>
       </c>
+      <c r="F84" t="s">
+        <v>75</v>
+      </c>
       <c r="H84" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I84" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="J84" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N84">
         <v>679.23</v>
@@ -6205,14 +6457,17 @@
       <c r="D85">
         <v>101.62</v>
       </c>
+      <c r="F85" t="s">
+        <v>75</v>
+      </c>
       <c r="H85" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I85" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="J85" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="N85">
         <v>464.650475685</v>
@@ -6249,14 +6504,17 @@
       <c r="D86">
         <v>101.62</v>
       </c>
+      <c r="F86" t="s">
+        <v>75</v>
+      </c>
       <c r="H86" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I86" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="J86" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="N86">
         <v>459.001012792</v>
@@ -6293,14 +6551,17 @@
       <c r="D87">
         <v>101.62</v>
       </c>
+      <c r="F87" t="s">
+        <v>75</v>
+      </c>
       <c r="H87" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I87" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="J87" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="N87">
         <v>435.318700827626</v>
@@ -6337,14 +6598,17 @@
       <c r="D88">
         <v>101.62</v>
       </c>
+      <c r="F88" t="s">
+        <v>75</v>
+      </c>
       <c r="H88" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I88" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="J88" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N88">
         <v>469.202</v>
@@ -6381,14 +6645,17 @@
       <c r="D89">
         <v>101.62</v>
       </c>
+      <c r="F89" t="s">
+        <v>75</v>
+      </c>
       <c r="H89" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I89" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="J89" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="N89">
         <v>412.587</v>
@@ -6425,14 +6692,17 @@
       <c r="D90">
         <v>101.62</v>
       </c>
+      <c r="F90" t="s">
+        <v>75</v>
+      </c>
       <c r="H90" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I90" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J90" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="N90">
         <v>384.701</v>
@@ -6469,14 +6739,17 @@
       <c r="D91">
         <v>101.62</v>
       </c>
+      <c r="F91" t="s">
+        <v>75</v>
+      </c>
       <c r="H91" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I91" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="J91" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N91">
         <v>386.64</v>
@@ -6513,14 +6786,17 @@
       <c r="D92">
         <v>101.62</v>
       </c>
+      <c r="F92" t="s">
+        <v>75</v>
+      </c>
       <c r="H92" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I92" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="J92" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="N92">
         <v>472.388</v>
@@ -6557,14 +6833,17 @@
       <c r="D93">
         <v>101.62</v>
       </c>
+      <c r="F93" t="s">
+        <v>75</v>
+      </c>
       <c r="H93" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I93" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="J93" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="N93">
         <v>305.870321755855</v>
@@ -6601,14 +6880,17 @@
       <c r="D94">
         <v>101.62</v>
       </c>
+      <c r="F94" t="s">
+        <v>75</v>
+      </c>
       <c r="H94" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I94" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="J94" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="N94">
         <v>277.538</v>
@@ -6645,14 +6927,17 @@
       <c r="D95">
         <v>101.62</v>
       </c>
+      <c r="F95" t="s">
+        <v>75</v>
+      </c>
       <c r="H95" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I95" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="J95" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="N95">
         <v>286.592</v>
@@ -6689,14 +6974,17 @@
       <c r="D96">
         <v>101.62</v>
       </c>
+      <c r="F96" t="s">
+        <v>75</v>
+      </c>
       <c r="H96" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I96" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J96" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="N96">
         <v>295.134</v>
@@ -6733,14 +7021,17 @@
       <c r="D97">
         <v>101.62</v>
       </c>
+      <c r="F97" t="s">
+        <v>75</v>
+      </c>
       <c r="H97" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I97" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J97" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="N97">
         <v>285.607</v>
@@ -6777,14 +7068,17 @@
       <c r="D98">
         <v>101.62</v>
       </c>
+      <c r="F98" t="s">
+        <v>75</v>
+      </c>
       <c r="H98" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I98" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="J98" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N98">
         <v>284.95</v>
@@ -6821,14 +7115,17 @@
       <c r="D99">
         <v>101.84</v>
       </c>
+      <c r="F99" t="s">
+        <v>75</v>
+      </c>
       <c r="H99" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I99" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="J99" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="N99">
         <v>171.479</v>
@@ -6865,14 +7162,17 @@
       <c r="D100">
         <v>101.84</v>
       </c>
+      <c r="F100" t="s">
+        <v>75</v>
+      </c>
       <c r="H100" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I100" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="J100" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="N100">
         <v>165.526</v>
@@ -6909,14 +7209,17 @@
       <c r="D101">
         <v>101.84</v>
       </c>
+      <c r="F101" t="s">
+        <v>75</v>
+      </c>
       <c r="H101" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I101" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="J101" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N101">
         <v>225.555</v>
@@ -6953,14 +7256,17 @@
       <c r="D102">
         <v>101.84</v>
       </c>
+      <c r="F102" t="s">
+        <v>75</v>
+      </c>
       <c r="H102" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I102" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="J102" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N102">
         <v>216.85</v>
@@ -6997,14 +7303,17 @@
       <c r="D103">
         <v>101.86</v>
       </c>
+      <c r="F103" t="s">
+        <v>75</v>
+      </c>
       <c r="H103" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I103" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="J103" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="N103">
         <v>208.79</v>
@@ -7041,14 +7350,17 @@
       <c r="D104">
         <v>101.86</v>
       </c>
+      <c r="F104" t="s">
+        <v>75</v>
+      </c>
       <c r="H104" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I104" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="J104" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="N104">
         <v>219.828</v>
@@ -7085,14 +7397,17 @@
       <c r="D105">
         <v>101.86</v>
       </c>
+      <c r="F105" t="s">
+        <v>75</v>
+      </c>
       <c r="H105" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I105" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="J105" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="N105">
         <v>207.09</v>
@@ -7129,14 +7444,17 @@
       <c r="D106">
         <v>101.86</v>
       </c>
+      <c r="F106" t="s">
+        <v>75</v>
+      </c>
       <c r="H106" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I106" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="J106" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N106">
         <v>208.84</v>
@@ -7173,14 +7491,17 @@
       <c r="D107">
         <v>101.86</v>
       </c>
+      <c r="F107" t="s">
+        <v>75</v>
+      </c>
       <c r="H107" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I107" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="J107" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N107">
         <v>218.153240305</v>
@@ -7217,14 +7538,17 @@
       <c r="D108">
         <v>101.86</v>
       </c>
+      <c r="F108" t="s">
+        <v>75</v>
+      </c>
       <c r="H108" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I108" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="J108" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="N108">
         <v>207.346458522</v>
@@ -7261,14 +7585,17 @@
       <c r="D109">
         <v>101.86</v>
       </c>
+      <c r="F109" t="s">
+        <v>75</v>
+      </c>
       <c r="H109" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I109" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="J109" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="N109">
         <v>212.81</v>
@@ -7305,14 +7632,17 @@
       <c r="D110">
         <v>101.86</v>
       </c>
+      <c r="F110" t="s">
+        <v>75</v>
+      </c>
       <c r="H110" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I110" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="J110" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="N110">
         <v>211.929</v>
@@ -7346,14 +7676,17 @@
       <c r="D111">
         <v>101.86</v>
       </c>
+      <c r="F111" t="s">
+        <v>75</v>
+      </c>
       <c r="H111" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I111" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="J111" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="N111">
         <v>257.716</v>
@@ -7387,14 +7720,17 @@
       <c r="D112">
         <v>101.86</v>
       </c>
+      <c r="F112" t="s">
+        <v>75</v>
+      </c>
       <c r="H112" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I112" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="J112" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="N112">
         <v>207.336</v>
@@ -7431,14 +7767,17 @@
       <c r="D113">
         <v>101.86</v>
       </c>
+      <c r="F113" t="s">
+        <v>75</v>
+      </c>
       <c r="H113" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I113" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="J113" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="N113">
         <v>170.878</v>
@@ -7475,14 +7814,17 @@
       <c r="D114">
         <v>101.86</v>
       </c>
+      <c r="F114" t="s">
+        <v>75</v>
+      </c>
       <c r="H114" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I114" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="J114" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N114">
         <v>167.189</v>
@@ -7519,14 +7861,17 @@
       <c r="D115">
         <v>101.86</v>
       </c>
+      <c r="F115" t="s">
+        <v>75</v>
+      </c>
       <c r="H115" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I115" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="J115" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="N115">
         <v>173.823</v>
@@ -7563,14 +7908,17 @@
       <c r="D116">
         <v>101.86</v>
       </c>
+      <c r="F116" t="s">
+        <v>75</v>
+      </c>
       <c r="H116" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I116" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="J116" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="N116">
         <v>151.26</v>
@@ -7607,14 +7955,17 @@
       <c r="D117">
         <v>101.86</v>
       </c>
+      <c r="F117" t="s">
+        <v>75</v>
+      </c>
       <c r="H117" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I117" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="J117" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="N117">
         <v>166.711</v>
@@ -7651,14 +8002,17 @@
       <c r="D118">
         <v>101.86</v>
       </c>
+      <c r="F118" t="s">
+        <v>75</v>
+      </c>
       <c r="H118" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I118" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="J118" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="N118">
         <v>163.071</v>
@@ -7695,14 +8049,17 @@
       <c r="D119">
         <v>101.87</v>
       </c>
+      <c r="F119" t="s">
+        <v>75</v>
+      </c>
       <c r="H119" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I119" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="J119" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="N119">
         <v>268.652933868259</v>
@@ -7739,14 +8096,17 @@
       <c r="D120">
         <v>101.87</v>
       </c>
+      <c r="F120" t="s">
+        <v>75</v>
+      </c>
       <c r="H120" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I120" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="J120" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="N120">
         <v>296.171</v>
@@ -7783,14 +8143,17 @@
       <c r="D121">
         <v>101.87</v>
       </c>
+      <c r="F121" t="s">
+        <v>75</v>
+      </c>
       <c r="H121" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I121" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="J121" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="N121">
         <v>294.151</v>
@@ -7827,14 +8190,17 @@
       <c r="D122">
         <v>101.87</v>
       </c>
+      <c r="F122" t="s">
+        <v>75</v>
+      </c>
       <c r="H122" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I122" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="J122" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N122">
         <v>307.473</v>
@@ -7871,14 +8237,17 @@
       <c r="D123">
         <v>101.87</v>
       </c>
+      <c r="F123" t="s">
+        <v>75</v>
+      </c>
       <c r="H123" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I123" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J123" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="N123">
         <v>273.227</v>
@@ -7915,14 +8284,17 @@
       <c r="D124">
         <v>101.87</v>
       </c>
+      <c r="F124" t="s">
+        <v>75</v>
+      </c>
       <c r="H124" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I124" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="J124" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N124">
         <v>250.779</v>
@@ -7959,14 +8331,17 @@
       <c r="D125">
         <v>101.87</v>
       </c>
+      <c r="F125" t="s">
+        <v>75</v>
+      </c>
       <c r="H125" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I125" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="J125" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="N125">
         <v>297.338</v>
@@ -8003,14 +8378,17 @@
       <c r="D126">
         <v>101.87</v>
       </c>
+      <c r="F126" t="s">
+        <v>75</v>
+      </c>
       <c r="H126" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I126" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="J126" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="N126">
         <v>179.578402708277</v>
@@ -8047,14 +8425,17 @@
       <c r="D127">
         <v>101.87</v>
       </c>
+      <c r="F127" t="s">
+        <v>75</v>
+      </c>
       <c r="H127" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I127" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J127" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="N127">
         <v>187.54</v>
@@ -8091,14 +8472,17 @@
       <c r="D128">
         <v>101.87</v>
       </c>
+      <c r="F128" t="s">
+        <v>75</v>
+      </c>
       <c r="H128" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I128" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="J128" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N128">
         <v>167.795</v>
@@ -8135,14 +8519,17 @@
       <c r="D129">
         <v>101.87</v>
       </c>
+      <c r="F129" t="s">
+        <v>75</v>
+      </c>
       <c r="H129" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I129" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J129" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N129">
         <v>165.618</v>
@@ -8179,14 +8566,17 @@
       <c r="D130">
         <v>101.87</v>
       </c>
+      <c r="F130" t="s">
+        <v>75</v>
+      </c>
       <c r="H130" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I130" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J130" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="N130">
         <v>169.914</v>
@@ -8223,14 +8613,17 @@
       <c r="D131">
         <v>101.87</v>
       </c>
+      <c r="F131" t="s">
+        <v>75</v>
+      </c>
       <c r="H131" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I131" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="J131" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="N131">
         <v>165.36</v>
@@ -8267,14 +8660,17 @@
       <c r="D132">
         <v>101.87</v>
       </c>
+      <c r="F132" t="s">
+        <v>75</v>
+      </c>
       <c r="H132" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I132" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J132" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="N132">
         <v>157.182</v>
@@ -8311,14 +8707,17 @@
       <c r="D133">
         <v>101.88</v>
       </c>
+      <c r="F133" t="s">
+        <v>75</v>
+      </c>
       <c r="H133" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I133" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J133" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="N133">
         <v>377.437</v>
@@ -8355,14 +8754,17 @@
       <c r="D134">
         <v>101.88</v>
       </c>
+      <c r="F134" t="s">
+        <v>75</v>
+      </c>
       <c r="H134" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I134" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J134" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="N134">
         <v>390.081</v>
@@ -8399,14 +8801,17 @@
       <c r="D135">
         <v>101.88</v>
       </c>
+      <c r="F135" t="s">
+        <v>75</v>
+      </c>
       <c r="H135" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I135" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="J135" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="N135">
         <v>378.652</v>
@@ -8443,14 +8848,17 @@
       <c r="D136">
         <v>101.88</v>
       </c>
+      <c r="F136" t="s">
+        <v>75</v>
+      </c>
       <c r="H136" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I136" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="J136" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="N136">
         <v>394.225</v>
@@ -8487,14 +8895,17 @@
       <c r="D137">
         <v>101.88</v>
       </c>
+      <c r="F137" t="s">
+        <v>75</v>
+      </c>
       <c r="H137" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I137" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J137" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N137">
         <v>282.342021043104</v>
@@ -8531,14 +8942,17 @@
       <c r="D138">
         <v>101.88</v>
       </c>
+      <c r="F138" t="s">
+        <v>75</v>
+      </c>
       <c r="H138" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I138" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="J138" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="N138">
         <v>326.873</v>
@@ -8575,14 +8989,17 @@
       <c r="D139">
         <v>101.88</v>
       </c>
+      <c r="F139" t="s">
+        <v>75</v>
+      </c>
       <c r="H139" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I139" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="J139" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="N139">
         <v>336.516</v>
@@ -8619,14 +9036,17 @@
       <c r="D140">
         <v>101.88</v>
       </c>
+      <c r="F140" t="s">
+        <v>75</v>
+      </c>
       <c r="H140" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I140" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J140" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N140">
         <v>312.11</v>
@@ -8663,14 +9083,17 @@
       <c r="D141">
         <v>101.88</v>
       </c>
+      <c r="F141" t="s">
+        <v>75</v>
+      </c>
       <c r="H141" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I141" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="J141" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="N141">
         <v>322.421</v>
@@ -8707,14 +9130,17 @@
       <c r="D142">
         <v>101.88</v>
       </c>
+      <c r="F142" t="s">
+        <v>75</v>
+      </c>
       <c r="H142" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I142" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="J142" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="N142">
         <v>290.267</v>
@@ -8751,14 +9177,17 @@
       <c r="D143">
         <v>101.95</v>
       </c>
+      <c r="F143" t="s">
+        <v>75</v>
+      </c>
       <c r="H143" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I143" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J143" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="N143">
         <v>150.532</v>
@@ -8795,14 +9224,17 @@
       <c r="D144">
         <v>101.95</v>
       </c>
+      <c r="F144" t="s">
+        <v>75</v>
+      </c>
       <c r="H144" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I144" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J144" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="N144">
         <v>150.67</v>
@@ -8839,14 +9271,17 @@
       <c r="D145">
         <v>101.95</v>
       </c>
+      <c r="F145" t="s">
+        <v>75</v>
+      </c>
       <c r="H145" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I145" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="J145" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="N145">
         <v>146.31</v>
@@ -8883,14 +9318,17 @@
       <c r="D146">
         <v>101.95</v>
       </c>
+      <c r="F146" t="s">
+        <v>75</v>
+      </c>
       <c r="H146" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I146" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="J146" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="N146">
         <v>157.07</v>
@@ -8927,14 +9365,17 @@
       <c r="D147">
         <v>101.95</v>
       </c>
+      <c r="F147" t="s">
+        <v>75</v>
+      </c>
       <c r="H147" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I147" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="J147" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="N147">
         <v>170.146027712</v>
@@ -8971,14 +9412,17 @@
       <c r="D148">
         <v>101.95</v>
       </c>
+      <c r="F148" t="s">
+        <v>75</v>
+      </c>
       <c r="H148" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I148" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="J148" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="N148">
         <v>156.117191958</v>
@@ -9015,14 +9459,17 @@
       <c r="D149">
         <v>101.95</v>
       </c>
+      <c r="F149" t="s">
+        <v>75</v>
+      </c>
       <c r="H149" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I149" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J149" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="N149">
         <v>159.277740416163</v>
@@ -9059,14 +9506,17 @@
       <c r="D150">
         <v>101.95</v>
       </c>
+      <c r="F150" t="s">
+        <v>75</v>
+      </c>
       <c r="H150" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I150" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="J150" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="N150">
         <v>144.144</v>
@@ -9103,14 +9553,17 @@
       <c r="D151">
         <v>101.95</v>
       </c>
+      <c r="F151" t="s">
+        <v>75</v>
+      </c>
       <c r="H151" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I151" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J151" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="N151">
         <v>158.282</v>
@@ -9147,14 +9600,17 @@
       <c r="D152">
         <v>101.95</v>
       </c>
+      <c r="F152" t="s">
+        <v>75</v>
+      </c>
       <c r="H152" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I152" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="J152" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="N152">
         <v>163.589</v>
@@ -9191,14 +9647,17 @@
       <c r="D153">
         <v>101.95</v>
       </c>
+      <c r="F153" t="s">
+        <v>75</v>
+      </c>
       <c r="H153" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I153" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="J153" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="N153">
         <v>134.733</v>
@@ -9235,14 +9694,17 @@
       <c r="D154">
         <v>101.95</v>
       </c>
+      <c r="F154" t="s">
+        <v>75</v>
+      </c>
       <c r="H154" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I154" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J154" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="N154">
         <v>155.581</v>
@@ -9279,14 +9741,17 @@
       <c r="D155">
         <v>101.95</v>
       </c>
+      <c r="F155" t="s">
+        <v>75</v>
+      </c>
       <c r="H155" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I155" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="J155" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="N155">
         <v>137.812</v>
@@ -9323,14 +9788,17 @@
       <c r="D156">
         <v>101.95</v>
       </c>
+      <c r="F156" t="s">
+        <v>75</v>
+      </c>
       <c r="H156" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I156" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J156" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="N156">
         <v>133.273</v>
@@ -9367,14 +9835,17 @@
       <c r="D157">
         <v>101.95</v>
       </c>
+      <c r="F157" t="s">
+        <v>75</v>
+      </c>
       <c r="H157" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I157" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="J157" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N157">
         <v>133.655</v>
@@ -9411,14 +9882,17 @@
       <c r="D158">
         <v>101.95</v>
       </c>
+      <c r="F158" t="s">
+        <v>75</v>
+      </c>
       <c r="H158" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I158" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="J158" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="N158">
         <v>131.668</v>
@@ -9455,14 +9929,17 @@
       <c r="D159">
         <v>101.95</v>
       </c>
+      <c r="F159" t="s">
+        <v>75</v>
+      </c>
       <c r="H159" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I159" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="J159" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="N159">
         <v>137.64</v>
@@ -9499,14 +9976,17 @@
       <c r="D160">
         <v>101.96</v>
       </c>
+      <c r="F160" t="s">
+        <v>75</v>
+      </c>
       <c r="H160" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I160" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="J160" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="N160">
         <v>510.82</v>
@@ -9543,14 +10023,17 @@
       <c r="D161">
         <v>101.96</v>
       </c>
+      <c r="F161" t="s">
+        <v>75</v>
+      </c>
       <c r="H161" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I161" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="J161" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="N161">
         <v>518.38</v>
@@ -9587,14 +10070,17 @@
       <c r="D162">
         <v>101.96</v>
       </c>
+      <c r="F162" t="s">
+        <v>75</v>
+      </c>
       <c r="H162" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I162" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="J162" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N162">
         <v>516.6799999999999</v>
@@ -9631,14 +10117,17 @@
       <c r="D163">
         <v>101.96</v>
       </c>
+      <c r="F163" t="s">
+        <v>75</v>
+      </c>
       <c r="H163" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I163" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="J163" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="N163">
         <v>507.94</v>
@@ -9675,14 +10164,17 @@
       <c r="D164">
         <v>101.96</v>
       </c>
+      <c r="F164" t="s">
+        <v>75</v>
+      </c>
       <c r="H164" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I164" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J164" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="N164">
         <v>513.624532465</v>
@@ -9719,14 +10211,17 @@
       <c r="D165">
         <v>101.96</v>
       </c>
+      <c r="F165" t="s">
+        <v>75</v>
+      </c>
       <c r="H165" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I165" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="J165" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="N165">
         <v>506.564477146</v>
@@ -9763,14 +10258,17 @@
       <c r="D166">
         <v>101.96</v>
       </c>
+      <c r="F166" t="s">
+        <v>75</v>
+      </c>
       <c r="H166" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I166" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="J166" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="N166">
         <v>501.990598536208</v>
@@ -9807,14 +10305,17 @@
       <c r="D167">
         <v>101.96</v>
       </c>
+      <c r="F167" t="s">
+        <v>75</v>
+      </c>
       <c r="H167" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I167" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="J167" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="N167">
         <v>513.324</v>
@@ -9851,14 +10352,17 @@
       <c r="D168">
         <v>101.96</v>
       </c>
+      <c r="F168" t="s">
+        <v>75</v>
+      </c>
       <c r="H168" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I168" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="J168" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="N168">
         <v>516.519</v>
@@ -9895,14 +10399,17 @@
       <c r="D169">
         <v>101.96</v>
       </c>
+      <c r="F169" t="s">
+        <v>75</v>
+      </c>
       <c r="H169" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I169" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="J169" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="N169">
         <v>506.757</v>
@@ -9939,14 +10446,17 @@
       <c r="D170">
         <v>101.96</v>
       </c>
+      <c r="F170" t="s">
+        <v>75</v>
+      </c>
       <c r="H170" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I170" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="J170" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="N170">
         <v>493.142</v>
@@ -9983,14 +10493,17 @@
       <c r="D171">
         <v>101.96</v>
       </c>
+      <c r="F171" t="s">
+        <v>75</v>
+      </c>
       <c r="H171" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I171" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="J171" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="N171">
         <v>511.2619999999999</v>
@@ -10027,14 +10540,17 @@
       <c r="D172">
         <v>101.96</v>
       </c>
+      <c r="F172" t="s">
+        <v>75</v>
+      </c>
       <c r="H172" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I172" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J172" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="N172">
         <v>506.1180000000001</v>
@@ -10071,14 +10587,17 @@
       <c r="D173">
         <v>101.96</v>
       </c>
+      <c r="F173" t="s">
+        <v>75</v>
+      </c>
       <c r="H173" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I173" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J173" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="N173">
         <v>520.561</v>
@@ -10115,14 +10634,17 @@
       <c r="D174">
         <v>101.96</v>
       </c>
+      <c r="F174" t="s">
+        <v>75</v>
+      </c>
       <c r="H174" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I174" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="J174" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="N174">
         <v>518.9110000000001</v>
@@ -10159,14 +10681,17 @@
       <c r="D175">
         <v>101.96</v>
       </c>
+      <c r="F175" t="s">
+        <v>75</v>
+      </c>
       <c r="H175" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I175" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="J175" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="N175">
         <v>505.442</v>
@@ -10203,14 +10728,17 @@
       <c r="D176">
         <v>101.96</v>
       </c>
+      <c r="F176" t="s">
+        <v>75</v>
+      </c>
       <c r="H176" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I176" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J176" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="N176">
         <v>526.635</v>
@@ -10247,14 +10775,17 @@
       <c r="D177">
         <v>101.96</v>
       </c>
+      <c r="F177" t="s">
+        <v>75</v>
+      </c>
       <c r="H177" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I177" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J177" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N177">
         <v>533.112</v>
@@ -10291,14 +10822,17 @@
       <c r="D178">
         <v>101.96</v>
       </c>
+      <c r="F178" t="s">
+        <v>75</v>
+      </c>
       <c r="H178" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I178" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="J178" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="N178">
         <v>108.193</v>
@@ -10335,14 +10869,17 @@
       <c r="D179">
         <v>101.96</v>
       </c>
+      <c r="F179" t="s">
+        <v>75</v>
+      </c>
       <c r="H179" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I179" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="J179" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="N179">
         <v>76.827</v>
@@ -10379,14 +10916,17 @@
       <c r="D180">
         <v>101.96</v>
       </c>
+      <c r="F180" t="s">
+        <v>75</v>
+      </c>
       <c r="H180" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I180" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="J180" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="N180">
         <v>37.775</v>
@@ -10423,14 +10963,17 @@
       <c r="D181">
         <v>101.96</v>
       </c>
+      <c r="F181" t="s">
+        <v>75</v>
+      </c>
       <c r="H181" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I181" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J181" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="N181">
         <v>102.324</v>
@@ -10467,14 +11010,17 @@
       <c r="D182">
         <v>101.96</v>
       </c>
+      <c r="F182" t="s">
+        <v>75</v>
+      </c>
       <c r="H182" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I182" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="J182" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N182">
         <v>90.949</v>
@@ -10511,14 +11057,17 @@
       <c r="D183">
         <v>101.96</v>
       </c>
+      <c r="F183" t="s">
+        <v>75</v>
+      </c>
       <c r="H183" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I183" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="J183" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="N183">
         <v>396.79</v>
@@ -10555,14 +11104,17 @@
       <c r="D184">
         <v>101.96</v>
       </c>
+      <c r="F184" t="s">
+        <v>75</v>
+      </c>
       <c r="H184" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I184" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="J184" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N184">
         <v>367.22</v>
@@ -10599,14 +11151,17 @@
       <c r="D185">
         <v>101.96</v>
       </c>
+      <c r="F185" t="s">
+        <v>75</v>
+      </c>
       <c r="H185" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I185" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="J185" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="N185">
         <v>367.4</v>
@@ -10643,14 +11198,17 @@
       <c r="D186">
         <v>101.96</v>
       </c>
+      <c r="F186" t="s">
+        <v>75</v>
+      </c>
       <c r="H186" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I186" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="J186" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="N186">
         <v>349.71</v>
@@ -10687,14 +11245,17 @@
       <c r="D187">
         <v>101.96</v>
       </c>
+      <c r="F187" t="s">
+        <v>75</v>
+      </c>
       <c r="H187" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I187" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J187" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N187">
         <v>381.816207208</v>
@@ -10731,14 +11292,17 @@
       <c r="D188">
         <v>101.96</v>
       </c>
+      <c r="F188" t="s">
+        <v>75</v>
+      </c>
       <c r="H188" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I188" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="J188" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="N188">
         <v>346.226290634</v>
@@ -10775,14 +11339,17 @@
       <c r="D189">
         <v>101.96</v>
       </c>
+      <c r="F189" t="s">
+        <v>75</v>
+      </c>
       <c r="H189" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I189" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="J189" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="N189">
         <v>314.14046557651</v>
@@ -10819,14 +11386,17 @@
       <c r="D190">
         <v>101.96</v>
       </c>
+      <c r="F190" t="s">
+        <v>75</v>
+      </c>
       <c r="H190" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I190" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="J190" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="N190">
         <v>324.841</v>
@@ -10863,14 +11433,17 @@
       <c r="D191">
         <v>101.96</v>
       </c>
+      <c r="F191" t="s">
+        <v>75</v>
+      </c>
       <c r="H191" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I191" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J191" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="N191">
         <v>345.792</v>
@@ -10907,14 +11480,17 @@
       <c r="D192">
         <v>101.96</v>
       </c>
+      <c r="F192" t="s">
+        <v>75</v>
+      </c>
       <c r="H192" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I192" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="J192" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="N192">
         <v>343.444</v>
@@ -10951,14 +11527,17 @@
       <c r="D193">
         <v>101.96</v>
       </c>
+      <c r="F193" t="s">
+        <v>75</v>
+      </c>
       <c r="H193" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I193" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="J193" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="N193">
         <v>319.744</v>
@@ -10995,14 +11574,17 @@
       <c r="D194">
         <v>101.96</v>
       </c>
+      <c r="F194" t="s">
+        <v>75</v>
+      </c>
       <c r="H194" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I194" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="J194" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="N194">
         <v>337</v>
@@ -11039,14 +11621,17 @@
       <c r="D195">
         <v>101.96</v>
       </c>
+      <c r="F195" t="s">
+        <v>75</v>
+      </c>
       <c r="H195" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I195" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="J195" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="N195">
         <v>303.414</v>
@@ -11083,14 +11668,17 @@
       <c r="D196">
         <v>101.96</v>
       </c>
+      <c r="F196" t="s">
+        <v>75</v>
+      </c>
       <c r="H196" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I196" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J196" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="N196">
         <v>337.248</v>
@@ -11127,14 +11715,17 @@
       <c r="D197">
         <v>101.96</v>
       </c>
+      <c r="F197" t="s">
+        <v>75</v>
+      </c>
       <c r="H197" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I197" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="J197" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="N197">
         <v>316.803</v>
@@ -11171,14 +11762,17 @@
       <c r="D198">
         <v>101.96</v>
       </c>
+      <c r="F198" t="s">
+        <v>75</v>
+      </c>
       <c r="H198" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I198" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="J198" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="N198">
         <v>314.231</v>
@@ -11215,14 +11809,17 @@
       <c r="D199">
         <v>101.96</v>
       </c>
+      <c r="F199" t="s">
+        <v>75</v>
+      </c>
       <c r="H199" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I199" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="J199" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N199">
         <v>326.368</v>
@@ -11259,14 +11856,17 @@
       <c r="D200">
         <v>101.96</v>
       </c>
+      <c r="F200" t="s">
+        <v>75</v>
+      </c>
       <c r="H200" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I200" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J200" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="N200">
         <v>958.228</v>
@@ -11303,14 +11903,17 @@
       <c r="D201">
         <v>102.03</v>
       </c>
+      <c r="F201" t="s">
+        <v>75</v>
+      </c>
       <c r="H201" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I201" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="J201" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="N201">
         <v>154.11</v>
@@ -11347,14 +11950,17 @@
       <c r="D202">
         <v>102.03</v>
       </c>
+      <c r="F202" t="s">
+        <v>75</v>
+      </c>
       <c r="H202" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I202" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="J202" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="N202">
         <v>156.498</v>
@@ -11391,14 +11997,17 @@
       <c r="D203">
         <v>102.03</v>
       </c>
+      <c r="F203" t="s">
+        <v>75</v>
+      </c>
       <c r="H203" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I203" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="J203" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="N203">
         <v>153.02</v>
@@ -11435,14 +12044,17 @@
       <c r="D204">
         <v>102.03</v>
       </c>
+      <c r="F204" t="s">
+        <v>75</v>
+      </c>
       <c r="H204" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I204" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="J204" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="N204">
         <v>150.44</v>
@@ -11479,14 +12091,17 @@
       <c r="D205">
         <v>102.03</v>
       </c>
+      <c r="F205" t="s">
+        <v>75</v>
+      </c>
       <c r="H205" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I205" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="J205" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="N205">
         <v>132.20865636</v>
@@ -11523,14 +12138,17 @@
       <c r="D206">
         <v>102.03</v>
       </c>
+      <c r="F206" t="s">
+        <v>75</v>
+      </c>
       <c r="H206" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I206" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="J206" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="N206">
         <v>186.929515528</v>
@@ -11567,14 +12185,17 @@
       <c r="D207">
         <v>102.03</v>
       </c>
+      <c r="F207" t="s">
+        <v>75</v>
+      </c>
       <c r="H207" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I207" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="J207" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="N207">
         <v>136.481863193713</v>
@@ -11611,14 +12232,17 @@
       <c r="D208">
         <v>102.03</v>
       </c>
+      <c r="F208" t="s">
+        <v>75</v>
+      </c>
       <c r="H208" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="I208" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="J208" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="N208">
         <v>189.06</v>
@@ -11655,14 +12279,17 @@
       <c r="D209">
         <v>102.03</v>
       </c>
+      <c r="F209" t="s">
+        <v>75</v>
+      </c>
       <c r="H209" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I209" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="J209" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="N209">
         <v>123.358</v>
@@ -11699,14 +12326,17 @@
       <c r="D210">
         <v>102.03</v>
       </c>
+      <c r="F210" t="s">
+        <v>75</v>
+      </c>
       <c r="H210" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I210" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="J210" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N210">
         <v>202.363</v>
@@ -11743,14 +12373,17 @@
       <c r="D211">
         <v>102.03</v>
       </c>
+      <c r="F211" t="s">
+        <v>75</v>
+      </c>
       <c r="H211" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I211" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="J211" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="N211">
         <v>136.444</v>
@@ -11787,14 +12420,17 @@
       <c r="D212">
         <v>102.03</v>
       </c>
+      <c r="F212" t="s">
+        <v>75</v>
+      </c>
       <c r="H212" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I212" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="J212" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N212">
         <v>191.47</v>
@@ -11831,14 +12467,17 @@
       <c r="D213">
         <v>102.03</v>
       </c>
+      <c r="F213" t="s">
+        <v>75</v>
+      </c>
       <c r="H213" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I213" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="J213" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="N213">
         <v>172.004</v>
@@ -11875,14 +12514,17 @@
       <c r="D214">
         <v>102.03</v>
       </c>
+      <c r="F214" t="s">
+        <v>75</v>
+      </c>
       <c r="H214" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I214" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="J214" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="N214">
         <v>102.585</v>
@@ -11919,14 +12561,17 @@
       <c r="D215">
         <v>102.03</v>
       </c>
+      <c r="F215" t="s">
+        <v>75</v>
+      </c>
       <c r="H215" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I215" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="J215" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="N215">
         <v>167.188</v>
@@ -11963,14 +12608,17 @@
       <c r="D216">
         <v>102.06</v>
       </c>
+      <c r="F216" t="s">
+        <v>75</v>
+      </c>
       <c r="H216" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I216" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="J216" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="N216">
         <v>422.66</v>
@@ -12007,14 +12655,17 @@
       <c r="D217">
         <v>102.06</v>
       </c>
+      <c r="F217" t="s">
+        <v>75</v>
+      </c>
       <c r="H217" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I217" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="J217" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="N217">
         <v>365.035</v>
@@ -12051,14 +12702,17 @@
       <c r="D218">
         <v>102.06</v>
       </c>
+      <c r="F218" t="s">
+        <v>75</v>
+      </c>
       <c r="H218" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I218" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="J218" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N218">
         <v>360.63</v>
@@ -12095,14 +12749,17 @@
       <c r="D219">
         <v>102.06</v>
       </c>
+      <c r="F219" t="s">
+        <v>75</v>
+      </c>
       <c r="H219" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I219" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="J219" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="N219">
         <v>303.1</v>
@@ -12139,14 +12796,17 @@
       <c r="D220">
         <v>102.06</v>
       </c>
+      <c r="F220" t="s">
+        <v>75</v>
+      </c>
       <c r="H220" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I220" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="J220" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="N220">
         <v>250.051349625</v>
@@ -12183,14 +12843,17 @@
       <c r="D221">
         <v>102.06</v>
       </c>
+      <c r="F221" t="s">
+        <v>75</v>
+      </c>
       <c r="H221" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I221" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="J221" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="N221">
         <v>281.241537682</v>
@@ -12227,14 +12890,17 @@
       <c r="D222">
         <v>102.06</v>
       </c>
+      <c r="F222" t="s">
+        <v>75</v>
+      </c>
       <c r="H222" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I222" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="J222" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="N222">
         <v>277.969045210475</v>
@@ -12271,14 +12937,17 @@
       <c r="D223">
         <v>102.06</v>
       </c>
+      <c r="F223" t="s">
+        <v>75</v>
+      </c>
       <c r="H223" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I223" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="J223" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="N223">
         <v>295.059</v>
@@ -12315,14 +12984,17 @@
       <c r="D224">
         <v>102.06</v>
       </c>
+      <c r="F224" t="s">
+        <v>75</v>
+      </c>
       <c r="H224" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I224" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="J224" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="N224">
         <v>308.06</v>
@@ -12359,14 +13031,17 @@
       <c r="D225">
         <v>102.06</v>
       </c>
+      <c r="F225" t="s">
+        <v>75</v>
+      </c>
       <c r="H225" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I225" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="J225" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="N225">
         <v>310.76</v>
@@ -12403,14 +13078,17 @@
       <c r="D226">
         <v>102.06</v>
       </c>
+      <c r="F226" t="s">
+        <v>75</v>
+      </c>
       <c r="H226" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="I226" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="J226" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="N226">
         <v>320.218</v>
@@ -12447,14 +13125,17 @@
       <c r="D227">
         <v>102.06</v>
       </c>
+      <c r="F227" t="s">
+        <v>75</v>
+      </c>
       <c r="H227" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I227" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="J227" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="N227">
         <v>310.937</v>
@@ -12491,14 +13172,17 @@
       <c r="D228">
         <v>102.06</v>
       </c>
+      <c r="F228" t="s">
+        <v>75</v>
+      </c>
       <c r="H228" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I228" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J228" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="N228">
         <v>343.27</v>
@@ -12535,14 +13219,17 @@
       <c r="D229">
         <v>102.06</v>
       </c>
+      <c r="F229" t="s">
+        <v>75</v>
+      </c>
       <c r="H229" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I229" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="J229" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N229">
         <v>334.269</v>
@@ -12579,14 +13266,17 @@
       <c r="D230">
         <v>102.06</v>
       </c>
+      <c r="F230" t="s">
+        <v>75</v>
+      </c>
       <c r="H230" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I230" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="J230" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N230">
         <v>304.194</v>
@@ -12623,14 +13313,17 @@
       <c r="D231">
         <v>102.1</v>
       </c>
+      <c r="F231" t="s">
+        <v>75</v>
+      </c>
       <c r="H231" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I231" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J231" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="N231">
         <v>48.74</v>
@@ -12667,14 +13360,17 @@
       <c r="D232">
         <v>102.1</v>
       </c>
+      <c r="F232" t="s">
+        <v>75</v>
+      </c>
       <c r="H232" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I232" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="J232" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="N232">
         <v>46.19</v>
@@ -12711,14 +13407,17 @@
       <c r="D233">
         <v>102.1</v>
       </c>
+      <c r="F233" t="s">
+        <v>75</v>
+      </c>
       <c r="H233" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I233" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="J233" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="N233">
         <v>46.29</v>
@@ -12755,14 +13454,17 @@
       <c r="D234">
         <v>102.1</v>
       </c>
+      <c r="F234" t="s">
+        <v>75</v>
+      </c>
       <c r="H234" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I234" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="J234" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="N234">
         <v>49.466434104</v>
@@ -12799,14 +13501,17 @@
       <c r="D235">
         <v>102.1</v>
       </c>
+      <c r="F235" t="s">
+        <v>75</v>
+      </c>
       <c r="H235" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I235" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="J235" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="N235">
         <v>47.794226816</v>
@@ -12843,14 +13548,17 @@
       <c r="D236">
         <v>102.1</v>
       </c>
+      <c r="F236" t="s">
+        <v>75</v>
+      </c>
       <c r="H236" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I236" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="J236" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="N236">
         <v>48.773</v>
@@ -12887,14 +13595,17 @@
       <c r="D237">
         <v>102.1</v>
       </c>
+      <c r="F237" t="s">
+        <v>75</v>
+      </c>
       <c r="H237" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I237" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="J237" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="N237">
         <v>58.763</v>
@@ -12931,14 +13642,17 @@
       <c r="D238">
         <v>102.1</v>
       </c>
+      <c r="F238" t="s">
+        <v>75</v>
+      </c>
       <c r="H238" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I238" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="J238" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="N238">
         <v>45.53899999999999</v>
@@ -12975,14 +13689,17 @@
       <c r="D239">
         <v>102.1</v>
       </c>
+      <c r="F239" t="s">
+        <v>75</v>
+      </c>
       <c r="H239" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="I239" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="J239" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="N239">
         <v>47.249</v>
@@ -13019,14 +13736,17 @@
       <c r="D240">
         <v>102.11</v>
       </c>
+      <c r="F240" t="s">
+        <v>75</v>
+      </c>
       <c r="H240" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="I240" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="J240" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N240">
         <v>108.43</v>
@@ -13063,14 +13783,17 @@
       <c r="D241">
         <v>102.11</v>
       </c>
+      <c r="F241" t="s">
+        <v>75</v>
+      </c>
       <c r="H241" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I241" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="J241" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="N241">
         <v>106.532</v>
@@ -13107,14 +13830,17 @@
       <c r="D242">
         <v>102.11</v>
       </c>
+      <c r="F242" t="s">
+        <v>75</v>
+      </c>
       <c r="H242" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I242" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="J242" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="N242">
         <v>107.62</v>
@@ -13151,14 +13877,17 @@
       <c r="D243">
         <v>102.11</v>
       </c>
+      <c r="F243" t="s">
+        <v>75</v>
+      </c>
       <c r="H243" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I243" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="J243" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="N243">
         <v>111.76</v>
@@ -13195,14 +13924,17 @@
       <c r="D244">
         <v>102.11</v>
       </c>
+      <c r="F244" t="s">
+        <v>75</v>
+      </c>
       <c r="H244" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I244" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="J244" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="N244">
         <v>111.677460768</v>
@@ -13239,14 +13971,17 @@
       <c r="D245">
         <v>102.11</v>
       </c>
+      <c r="F245" t="s">
+        <v>75</v>
+      </c>
       <c r="H245" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I245" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="J245" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="N245">
         <v>92.700091008</v>
@@ -13283,14 +14018,17 @@
       <c r="D246">
         <v>102.11</v>
       </c>
+      <c r="F246" t="s">
+        <v>75</v>
+      </c>
       <c r="H246" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I246" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="J246" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="N246">
         <v>78.57781268330039</v>
@@ -13327,14 +14065,17 @@
       <c r="D247">
         <v>102.11</v>
       </c>
+      <c r="F247" t="s">
+        <v>75</v>
+      </c>
       <c r="H247" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I247" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="J247" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="N247">
         <v>82.334</v>
@@ -13371,14 +14112,17 @@
       <c r="D248">
         <v>102.11</v>
       </c>
+      <c r="F248" t="s">
+        <v>75</v>
+      </c>
       <c r="H248" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I248" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="J248" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="N248">
         <v>84.38200000000001</v>
@@ -13415,14 +14159,17 @@
       <c r="D249">
         <v>102.11</v>
       </c>
+      <c r="F249" t="s">
+        <v>75</v>
+      </c>
       <c r="H249" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I249" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="J249" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="N249">
         <v>96.627</v>
@@ -13459,14 +14206,17 @@
       <c r="D250">
         <v>102.11</v>
       </c>
+      <c r="F250" t="s">
+        <v>75</v>
+      </c>
       <c r="H250" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I250" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="J250" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="N250">
         <v>94.995</v>
@@ -13503,14 +14253,17 @@
       <c r="D251">
         <v>102.11</v>
       </c>
+      <c r="F251" t="s">
+        <v>75</v>
+      </c>
       <c r="H251" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I251" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="J251" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="N251">
         <v>77.114</v>
@@ -13547,14 +14300,17 @@
       <c r="D252">
         <v>102.11</v>
       </c>
+      <c r="F252" t="s">
+        <v>75</v>
+      </c>
       <c r="H252" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I252" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J252" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="N252">
         <v>119.628</v>
@@ -13591,14 +14347,17 @@
       <c r="D253">
         <v>102.11</v>
       </c>
+      <c r="F253" t="s">
+        <v>75</v>
+      </c>
       <c r="H253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I253" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="J253" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="N253">
         <v>117.666</v>
@@ -13635,14 +14394,17 @@
       <c r="D254">
         <v>102.14</v>
       </c>
+      <c r="F254" t="s">
+        <v>75</v>
+      </c>
       <c r="H254" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I254" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="J254" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N254">
         <v>326.227</v>
@@ -13679,14 +14441,17 @@
       <c r="D255">
         <v>102.14</v>
       </c>
+      <c r="F255" t="s">
+        <v>75</v>
+      </c>
       <c r="H255" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="I255" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="J255" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="N255">
         <v>334.526</v>
@@ -13723,14 +14488,17 @@
       <c r="D256">
         <v>102.14</v>
       </c>
+      <c r="F256" t="s">
+        <v>75</v>
+      </c>
       <c r="H256" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I256" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="J256" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="N256">
         <v>328.381</v>
@@ -13767,14 +14535,17 @@
       <c r="D257">
         <v>102.14</v>
       </c>
+      <c r="F257" t="s">
+        <v>75</v>
+      </c>
       <c r="H257" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I257" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J257" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="N257">
         <v>351.15</v>
@@ -13811,14 +14582,17 @@
       <c r="D258">
         <v>102.14</v>
       </c>
+      <c r="F258" t="s">
+        <v>75</v>
+      </c>
       <c r="H258" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I258" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="J258" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N258">
         <v>322.656</v>
@@ -13855,14 +14629,17 @@
       <c r="D259">
         <v>102.14</v>
       </c>
+      <c r="F259" t="s">
+        <v>75</v>
+      </c>
       <c r="H259" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I259" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="J259" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="N259">
         <v>302.997</v>
@@ -13899,14 +14676,17 @@
       <c r="D260">
         <v>102.14</v>
       </c>
+      <c r="F260" t="s">
+        <v>75</v>
+      </c>
       <c r="H260" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I260" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="J260" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="N260">
         <v>76.93000000000001</v>
@@ -13943,14 +14723,17 @@
       <c r="D261">
         <v>102.14</v>
       </c>
+      <c r="F261" t="s">
+        <v>75</v>
+      </c>
       <c r="H261" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I261" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="J261" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="N261">
         <v>73.37</v>
@@ -13987,14 +14770,17 @@
       <c r="D262">
         <v>102.14</v>
       </c>
+      <c r="F262" t="s">
+        <v>75</v>
+      </c>
       <c r="H262" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I262" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="J262" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="N262">
         <v>79.12</v>
@@ -14031,14 +14817,17 @@
       <c r="D263">
         <v>102.14</v>
       </c>
+      <c r="F263" t="s">
+        <v>75</v>
+      </c>
       <c r="H263" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I263" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="J263" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="N263">
         <v>79.11</v>
@@ -14075,14 +14864,17 @@
       <c r="D264">
         <v>102.14</v>
       </c>
+      <c r="F264" t="s">
+        <v>75</v>
+      </c>
       <c r="H264" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I264" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="J264" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="N264">
         <v>86.326364056</v>
@@ -14119,14 +14911,17 @@
       <c r="D265">
         <v>102.14</v>
       </c>
+      <c r="F265" t="s">
+        <v>75</v>
+      </c>
       <c r="H265" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I265" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="J265" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="N265">
         <v>79.875318166</v>
@@ -14163,14 +14958,17 @@
       <c r="D266">
         <v>102.14</v>
       </c>
+      <c r="F266" t="s">
+        <v>75</v>
+      </c>
       <c r="H266" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I266" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="J266" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="N266">
         <v>80.6236034880382</v>
@@ -14207,14 +15005,17 @@
       <c r="D267">
         <v>102.14</v>
       </c>
+      <c r="F267" t="s">
+        <v>75</v>
+      </c>
       <c r="H267" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I267" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J267" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="N267">
         <v>87.71699999999998</v>
@@ -14251,14 +15052,17 @@
       <c r="D268">
         <v>102.14</v>
       </c>
+      <c r="F268" t="s">
+        <v>75</v>
+      </c>
       <c r="H268" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="I268" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="J268" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="N268">
         <v>73.208</v>
@@ -14295,14 +15099,17 @@
       <c r="D269">
         <v>102.14</v>
       </c>
+      <c r="F269" t="s">
+        <v>75</v>
+      </c>
       <c r="H269" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I269" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="J269" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="N269">
         <v>115.402</v>
@@ -14339,14 +15146,17 @@
       <c r="D270">
         <v>102.22</v>
       </c>
+      <c r="F270" t="s">
+        <v>75</v>
+      </c>
       <c r="H270" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I270" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="J270" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="N270">
         <v>38.6</v>
@@ -14383,14 +15193,17 @@
       <c r="D271">
         <v>102.22</v>
       </c>
+      <c r="F271" t="s">
+        <v>75</v>
+      </c>
       <c r="H271" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="I271" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="J271" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="N271">
         <v>37.61</v>
@@ -14427,14 +15240,17 @@
       <c r="D272">
         <v>102.22</v>
       </c>
+      <c r="F272" t="s">
+        <v>75</v>
+      </c>
       <c r="H272" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="I272" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="J272" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="N272">
         <v>35.14</v>
@@ -14471,14 +15287,17 @@
       <c r="D273">
         <v>102.22</v>
       </c>
+      <c r="F273" t="s">
+        <v>75</v>
+      </c>
       <c r="H273" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="I273" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="J273" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="N273">
         <v>36.487003296</v>
@@ -14515,14 +15334,17 @@
       <c r="D274">
         <v>102.22</v>
       </c>
+      <c r="F274" t="s">
+        <v>75</v>
+      </c>
       <c r="H274" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I274" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="J274" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="N274">
         <v>34.978820716</v>
@@ -14559,14 +15381,17 @@
       <c r="D275">
         <v>102.22</v>
       </c>
+      <c r="F275" t="s">
+        <v>75</v>
+      </c>
       <c r="H275" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I275" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="J275" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="N275">
         <v>35.8596279774078</v>
@@ -14603,14 +15428,17 @@
       <c r="D276">
         <v>102.22</v>
       </c>
+      <c r="F276" t="s">
+        <v>75</v>
+      </c>
       <c r="H276" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I276" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="J276" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="N276">
         <v>35.25</v>
@@ -14647,14 +15475,17 @@
       <c r="D277">
         <v>102.22</v>
       </c>
+      <c r="F277" t="s">
+        <v>75</v>
+      </c>
       <c r="H277" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I277" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="J277" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="N277">
         <v>35.289</v>
@@ -14691,14 +15522,17 @@
       <c r="D278">
         <v>102.22</v>
       </c>
+      <c r="F278" t="s">
+        <v>75</v>
+      </c>
       <c r="H278" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I278" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="J278" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="N278">
         <v>33.985</v>
@@ -14735,14 +15569,17 @@
       <c r="D279">
         <v>102.22</v>
       </c>
+      <c r="F279" t="s">
+        <v>75</v>
+      </c>
       <c r="H279" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I279" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="J279" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="N279">
         <v>35.828</v>
@@ -14779,14 +15616,17 @@
       <c r="D280">
         <v>102.22</v>
       </c>
+      <c r="F280" t="s">
+        <v>75</v>
+      </c>
       <c r="H280" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I280" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="J280" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="N280">
         <v>36.786</v>
@@ -14811,6 +15651,11 @@
       </c>
       <c r="AD280">
         <v>10</v>
+      </c>
+    </row>
+    <row r="281" spans="2:30">
+      <c r="F281" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/MDPI-Xianshuihe_Datenbank/before_conversion_xian_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/MDPI-Xianshuihe_Datenbank/before_conversion_xian_mapped_readable.xlsx
@@ -15657,6 +15657,9 @@
       <c r="F281" t="s">
         <v>75</v>
       </c>
+      <c r="AD281">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
